--- a/issues/728-token-budget-estimation/data/敏捷软件开发AI应用需求情况统计.xlsx
+++ b/issues/728-token-budget-estimation/data/敏捷软件开发AI应用需求情况统计.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/suwei/workspace/astra-flow/poc/issues/728-token-budget-estimation/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F7213E9D-33C1-CD4A-B8A8-3162FD6267FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01ED2F40-AA58-F94C-97A9-35859CF6EFAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="2" xr2:uid="{752BAC88-3D22-6345-9E5D-6A586CA68B77}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" xr2:uid="{752BAC88-3D22-6345-9E5D-6A586CA68B77}"/>
   </bookViews>
   <sheets>
     <sheet name="应用产品" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="334">
   <si>
     <t>序号</t>
   </si>
@@ -1122,6 +1122,10 @@
   <si>
     <t>费用情况
 （元/人/月）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>合计</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1732,7 +1736,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1770,13 +1774,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1945,6 +1960,159 @@
     <xf numFmtId="0" fontId="77" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1963,164 +2131,14 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="87" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2447,50 +2465,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" s="3" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="109" t="s">
         <v>313</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="56" t="s">
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="107" t="s">
         <v>315</v>
       </c>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="57"/>
-      <c r="N1" s="61" t="s">
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
+      <c r="I1" s="108"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="112" t="s">
         <v>316</v>
       </c>
-      <c r="O1" s="57"/>
-      <c r="P1" s="57"/>
-      <c r="Q1" s="57"/>
-      <c r="R1" s="57"/>
-      <c r="S1" s="57"/>
-      <c r="T1" s="57"/>
-      <c r="U1" s="60" t="s">
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="111" t="s">
         <v>317</v>
       </c>
-      <c r="V1" s="57"/>
-      <c r="W1" s="57"/>
-      <c r="X1" s="57"/>
-      <c r="Y1" s="57"/>
-      <c r="Z1" s="57"/>
-      <c r="AA1" s="57"/>
-      <c r="AB1" s="56" t="s">
+      <c r="V1" s="108"/>
+      <c r="W1" s="108"/>
+      <c r="X1" s="108"/>
+      <c r="Y1" s="108"/>
+      <c r="Z1" s="108"/>
+      <c r="AA1" s="108"/>
+      <c r="AB1" s="107" t="s">
         <v>319</v>
       </c>
-      <c r="AC1" s="57"/>
-      <c r="AD1" s="57"/>
-      <c r="AE1" s="57"/>
-      <c r="AF1" s="57"/>
-      <c r="AG1" s="57"/>
-      <c r="AH1" s="57"/>
+      <c r="AC1" s="108"/>
+      <c r="AD1" s="108"/>
+      <c r="AE1" s="108"/>
+      <c r="AF1" s="108"/>
+      <c r="AG1" s="108"/>
+      <c r="AH1" s="108"/>
     </row>
     <row r="2" spans="1:34" s="3" customFormat="1" ht="41.25" customHeight="1">
       <c r="A2" s="4" t="s">
@@ -3105,7 +3123,9 @@
       </c>
       <c r="AB7" s="15"/>
       <c r="AC7" s="15"/>
-      <c r="AD7" s="15"/>
+      <c r="AD7" s="15" t="s">
+        <v>33</v>
+      </c>
       <c r="AE7" s="15"/>
       <c r="AF7" s="15">
         <v>200</v>
@@ -3420,7 +3440,7 @@
         <v>0</v>
       </c>
       <c r="AD10" s="15" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="AE10" s="15"/>
       <c r="AF10" s="15">
@@ -4313,6 +4333,9 @@
       <c r="AH19" s="15"/>
     </row>
     <row r="20" spans="1:34" ht="41.25" customHeight="1">
+      <c r="A20" t="s">
+        <v>333</v>
+      </c>
       <c r="L20">
         <f>SUM(L3:L19)</f>
         <v>46</v>
@@ -4384,26 +4407,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="112" t="s">
         <v>323</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="64" t="s">
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="108"/>
+      <c r="G1" s="108"/>
+      <c r="H1" s="113" t="s">
         <v>324</v>
       </c>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="57"/>
-      <c r="N1" s="57"/>
-    </row>
-    <row r="2" spans="1:14" ht="42">
+      <c r="I1" s="108"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+    </row>
+    <row r="2" spans="1:14" ht="28">
       <c r="A2" s="6" t="s">
         <v>13</v>
       </c>
@@ -4413,7 +4436,7 @@
       <c r="C2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="65" t="s">
+      <c r="D2" s="57" t="s">
         <v>322</v>
       </c>
       <c r="E2" s="6" t="s">
@@ -4425,25 +4448,25 @@
       <c r="G2" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="H2" s="66" t="s">
+      <c r="H2" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="66" t="s">
+      <c r="I2" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="66" t="s">
+      <c r="J2" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="K2" s="67" t="s">
+      <c r="K2" s="58" t="s">
         <v>322</v>
       </c>
-      <c r="L2" s="66" t="s">
+      <c r="L2" s="56" t="s">
         <v>332</v>
       </c>
-      <c r="M2" s="66" t="s">
+      <c r="M2" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="68" t="s">
+      <c r="N2" s="59" t="s">
         <v>12</v>
       </c>
     </row>
@@ -4454,7 +4477,7 @@
       <c r="B3" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="69" t="s">
+      <c r="C3" s="60" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="19">
@@ -4470,25 +4493,25 @@
         <f t="shared" ref="G3:G23" si="0">E3*F3</f>
         <v>18000</v>
       </c>
-      <c r="H3" s="70" t="s">
+      <c r="H3" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="70" t="s">
+      <c r="I3" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="71" t="s">
+      <c r="J3" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="70">
+      <c r="K3" s="61">
         <v>1200</v>
       </c>
-      <c r="L3" s="70">
+      <c r="L3" s="61">
         <v>0</v>
       </c>
-      <c r="M3" s="70">
+      <c r="M3" s="61">
         <v>18</v>
       </c>
-      <c r="N3" s="70">
+      <c r="N3" s="61">
         <f t="shared" ref="N3:N23" si="1">L3*M3</f>
         <v>0</v>
       </c>
@@ -4500,7 +4523,7 @@
       <c r="B4" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="72" t="s">
+      <c r="C4" s="63" t="s">
         <v>29</v>
       </c>
       <c r="D4" s="19">
@@ -4516,25 +4539,25 @@
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="H4" s="70" t="s">
+      <c r="H4" s="61" t="s">
         <v>28</v>
       </c>
-      <c r="I4" s="70" t="s">
+      <c r="I4" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="J4" s="73" t="s">
+      <c r="J4" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="K4" s="70">
+      <c r="K4" s="61">
         <v>1200</v>
       </c>
-      <c r="L4" s="70">
+      <c r="L4" s="61">
         <v>0</v>
       </c>
-      <c r="M4" s="70">
+      <c r="M4" s="61">
         <v>3</v>
       </c>
-      <c r="N4" s="70">
+      <c r="N4" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4546,7 +4569,7 @@
       <c r="B5" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="74" t="s">
+      <c r="C5" s="65" t="s">
         <v>35</v>
       </c>
       <c r="D5" s="19">
@@ -4562,25 +4585,25 @@
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="H5" s="70" t="s">
+      <c r="H5" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="I5" s="70" t="s">
+      <c r="I5" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="75" t="s">
+      <c r="J5" s="66" t="s">
         <v>35</v>
       </c>
-      <c r="K5" s="70">
+      <c r="K5" s="61">
         <v>1200</v>
       </c>
-      <c r="L5" s="70">
+      <c r="L5" s="61">
         <v>0</v>
       </c>
-      <c r="M5" s="70">
+      <c r="M5" s="61">
         <v>3</v>
       </c>
-      <c r="N5" s="70">
+      <c r="N5" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4592,7 +4615,7 @@
       <c r="B6" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="76" t="s">
+      <c r="C6" s="67" t="s">
         <v>38</v>
       </c>
       <c r="D6" s="19">
@@ -4608,25 +4631,25 @@
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="H6" s="70" t="s">
+      <c r="H6" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="I6" s="70" t="s">
+      <c r="I6" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="J6" s="77" t="s">
+      <c r="J6" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="K6" s="70">
+      <c r="K6" s="61">
         <v>1200</v>
       </c>
-      <c r="L6" s="70">
+      <c r="L6" s="61">
         <v>0</v>
       </c>
-      <c r="M6" s="70">
+      <c r="M6" s="61">
         <v>3</v>
       </c>
-      <c r="N6" s="70">
+      <c r="N6" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4638,7 +4661,7 @@
       <c r="B7" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="78" t="s">
+      <c r="C7" s="69" t="s">
         <v>43</v>
       </c>
       <c r="D7" s="19">
@@ -4654,25 +4677,25 @@
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="H7" s="70" t="s">
+      <c r="H7" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="I7" s="70" t="s">
+      <c r="I7" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="J7" s="79" t="s">
+      <c r="J7" s="70" t="s">
         <v>43</v>
       </c>
-      <c r="K7" s="70">
+      <c r="K7" s="61">
         <v>1200</v>
       </c>
-      <c r="L7" s="70">
+      <c r="L7" s="61">
         <v>0</v>
       </c>
-      <c r="M7" s="70">
+      <c r="M7" s="61">
         <v>3</v>
       </c>
-      <c r="N7" s="70">
+      <c r="N7" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4684,7 +4707,7 @@
       <c r="B8" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="80" t="s">
+      <c r="C8" s="71" t="s">
         <v>47</v>
       </c>
       <c r="D8" s="19">
@@ -4700,25 +4723,25 @@
         <f t="shared" si="0"/>
         <v>9000</v>
       </c>
-      <c r="H8" s="70" t="s">
+      <c r="H8" s="61" t="s">
         <v>46</v>
       </c>
-      <c r="I8" s="70" t="s">
+      <c r="I8" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="J8" s="81" t="s">
+      <c r="J8" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="K8" s="70">
+      <c r="K8" s="61">
         <v>1200</v>
       </c>
-      <c r="L8" s="70">
+      <c r="L8" s="61">
         <v>0</v>
       </c>
-      <c r="M8" s="70">
+      <c r="M8" s="61">
         <v>9</v>
       </c>
-      <c r="N8" s="70">
+      <c r="N8" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4730,7 +4753,7 @@
       <c r="B9" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="82" t="s">
+      <c r="C9" s="73" t="s">
         <v>51</v>
       </c>
       <c r="D9" s="19">
@@ -4746,25 +4769,25 @@
         <f t="shared" si="0"/>
         <v>9000</v>
       </c>
-      <c r="H9" s="70" t="s">
+      <c r="H9" s="61" t="s">
         <v>50</v>
       </c>
-      <c r="I9" s="70" t="s">
+      <c r="I9" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="J9" s="83" t="s">
+      <c r="J9" s="74" t="s">
         <v>51</v>
       </c>
-      <c r="K9" s="70">
+      <c r="K9" s="61">
         <v>1200</v>
       </c>
-      <c r="L9" s="70">
+      <c r="L9" s="61">
         <v>0</v>
       </c>
-      <c r="M9" s="70">
+      <c r="M9" s="61">
         <v>9</v>
       </c>
-      <c r="N9" s="70">
+      <c r="N9" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4776,7 +4799,7 @@
       <c r="B10" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="84" t="s">
+      <c r="C10" s="75" t="s">
         <v>58</v>
       </c>
       <c r="D10" s="19">
@@ -4792,25 +4815,25 @@
         <f t="shared" si="0"/>
         <v>6000</v>
       </c>
-      <c r="H10" s="70" t="s">
+      <c r="H10" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="I10" s="70" t="s">
+      <c r="I10" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="J10" s="85" t="s">
+      <c r="J10" s="76" t="s">
         <v>58</v>
       </c>
-      <c r="K10" s="70">
+      <c r="K10" s="61">
         <v>1200</v>
       </c>
-      <c r="L10" s="70">
+      <c r="L10" s="61">
         <v>0</v>
       </c>
-      <c r="M10" s="70">
+      <c r="M10" s="61">
         <v>6</v>
       </c>
-      <c r="N10" s="70">
+      <c r="N10" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4822,7 +4845,7 @@
       <c r="B11" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="86" t="s">
+      <c r="C11" s="77" t="s">
         <v>62</v>
       </c>
       <c r="D11" s="19">
@@ -4838,25 +4861,25 @@
         <f t="shared" si="0"/>
         <v>5000</v>
       </c>
-      <c r="H11" s="70" t="s">
+      <c r="H11" s="61" t="s">
         <v>61</v>
       </c>
-      <c r="I11" s="70" t="s">
+      <c r="I11" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="J11" s="87" t="s">
+      <c r="J11" s="78" t="s">
         <v>62</v>
       </c>
-      <c r="K11" s="70">
+      <c r="K11" s="61">
         <v>1200</v>
       </c>
-      <c r="L11" s="70">
+      <c r="L11" s="61">
         <v>0</v>
       </c>
-      <c r="M11" s="70">
+      <c r="M11" s="61">
         <v>5</v>
       </c>
-      <c r="N11" s="70">
+      <c r="N11" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4868,7 +4891,7 @@
       <c r="B12" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="88" t="s">
+      <c r="C12" s="79" t="s">
         <v>67</v>
       </c>
       <c r="D12" s="19">
@@ -4884,25 +4907,25 @@
         <f t="shared" si="0"/>
         <v>8000</v>
       </c>
-      <c r="H12" s="70" t="s">
+      <c r="H12" s="61" t="s">
         <v>66</v>
       </c>
-      <c r="I12" s="70" t="s">
+      <c r="I12" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="J12" s="89" t="s">
+      <c r="J12" s="80" t="s">
         <v>67</v>
       </c>
-      <c r="K12" s="70">
+      <c r="K12" s="61">
         <v>1200</v>
       </c>
-      <c r="L12" s="70">
+      <c r="L12" s="61">
         <v>0</v>
       </c>
-      <c r="M12" s="70">
+      <c r="M12" s="61">
         <v>8</v>
       </c>
-      <c r="N12" s="70">
+      <c r="N12" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4914,7 +4937,7 @@
       <c r="B13" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="90" t="s">
+      <c r="C13" s="81" t="s">
         <v>72</v>
       </c>
       <c r="D13" s="19">
@@ -4930,25 +4953,25 @@
         <f t="shared" si="0"/>
         <v>8000</v>
       </c>
-      <c r="H13" s="70" t="s">
+      <c r="H13" s="61" t="s">
         <v>71</v>
       </c>
-      <c r="I13" s="70" t="s">
+      <c r="I13" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="J13" s="91" t="s">
+      <c r="J13" s="82" t="s">
         <v>72</v>
       </c>
-      <c r="K13" s="70">
+      <c r="K13" s="61">
         <v>1200</v>
       </c>
-      <c r="L13" s="70">
+      <c r="L13" s="61">
         <v>0</v>
       </c>
-      <c r="M13" s="70">
+      <c r="M13" s="61">
         <v>8</v>
       </c>
-      <c r="N13" s="70">
+      <c r="N13" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4960,7 +4983,7 @@
       <c r="B14" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="92" t="s">
+      <c r="C14" s="83" t="s">
         <v>75</v>
       </c>
       <c r="D14" s="19">
@@ -4976,25 +4999,25 @@
         <f t="shared" si="0"/>
         <v>8000</v>
       </c>
-      <c r="H14" s="70" t="s">
+      <c r="H14" s="61" t="s">
         <v>74</v>
       </c>
-      <c r="I14" s="70" t="s">
+      <c r="I14" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="J14" s="93" t="s">
+      <c r="J14" s="84" t="s">
         <v>75</v>
       </c>
-      <c r="K14" s="70">
+      <c r="K14" s="61">
         <v>1200</v>
       </c>
-      <c r="L14" s="70">
+      <c r="L14" s="61">
         <v>0</v>
       </c>
-      <c r="M14" s="70">
+      <c r="M14" s="61">
         <v>8</v>
       </c>
-      <c r="N14" s="70">
+      <c r="N14" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5006,7 +5029,7 @@
       <c r="B15" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="94" t="s">
+      <c r="C15" s="85" t="s">
         <v>78</v>
       </c>
       <c r="D15" s="19">
@@ -5022,25 +5045,25 @@
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="H15" s="70" t="s">
+      <c r="H15" s="61" t="s">
         <v>77</v>
       </c>
-      <c r="I15" s="70" t="s">
+      <c r="I15" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="95" t="s">
+      <c r="J15" s="86" t="s">
         <v>78</v>
       </c>
-      <c r="K15" s="70">
+      <c r="K15" s="61">
         <v>1200</v>
       </c>
-      <c r="L15" s="70">
+      <c r="L15" s="61">
         <v>0</v>
       </c>
-      <c r="M15" s="70">
+      <c r="M15" s="61">
         <v>3</v>
       </c>
-      <c r="N15" s="70">
+      <c r="N15" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5052,7 +5075,7 @@
       <c r="B16" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="96" t="s">
+      <c r="C16" s="87" t="s">
         <v>81</v>
       </c>
       <c r="D16" s="19">
@@ -5068,25 +5091,25 @@
         <f t="shared" si="0"/>
         <v>10000</v>
       </c>
-      <c r="H16" s="70" t="s">
+      <c r="H16" s="61" t="s">
         <v>80</v>
       </c>
-      <c r="I16" s="70" t="s">
+      <c r="I16" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="J16" s="97" t="s">
+      <c r="J16" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="K16" s="70">
+      <c r="K16" s="61">
         <v>1200</v>
       </c>
-      <c r="L16" s="70">
+      <c r="L16" s="61">
         <v>0</v>
       </c>
-      <c r="M16" s="70">
+      <c r="M16" s="61">
         <v>10</v>
       </c>
-      <c r="N16" s="70">
+      <c r="N16" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5098,7 +5121,7 @@
       <c r="B17" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="98" t="s">
+      <c r="C17" s="89" t="s">
         <v>85</v>
       </c>
       <c r="D17" s="19">
@@ -5114,25 +5137,25 @@
         <f t="shared" si="0"/>
         <v>4000</v>
       </c>
-      <c r="H17" s="70" t="s">
+      <c r="H17" s="61" t="s">
         <v>84</v>
       </c>
-      <c r="I17" s="70" t="s">
+      <c r="I17" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="J17" s="99" t="s">
+      <c r="J17" s="90" t="s">
         <v>85</v>
       </c>
-      <c r="K17" s="70">
+      <c r="K17" s="61">
         <v>1200</v>
       </c>
-      <c r="L17" s="70">
+      <c r="L17" s="61">
         <v>0</v>
       </c>
-      <c r="M17" s="70">
+      <c r="M17" s="61">
         <v>4</v>
       </c>
-      <c r="N17" s="70">
+      <c r="N17" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5144,7 +5167,7 @@
       <c r="B18" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="100" t="s">
+      <c r="C18" s="91" t="s">
         <v>90</v>
       </c>
       <c r="D18" s="19">
@@ -5160,25 +5183,25 @@
         <f t="shared" si="0"/>
         <v>4000</v>
       </c>
-      <c r="H18" s="70" t="s">
+      <c r="H18" s="61" t="s">
         <v>89</v>
       </c>
-      <c r="I18" s="70" t="s">
+      <c r="I18" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="J18" s="101" t="s">
+      <c r="J18" s="92" t="s">
         <v>90</v>
       </c>
-      <c r="K18" s="70">
+      <c r="K18" s="61">
         <v>1200</v>
       </c>
-      <c r="L18" s="70">
+      <c r="L18" s="61">
         <v>0</v>
       </c>
-      <c r="M18" s="70">
+      <c r="M18" s="61">
         <v>4</v>
       </c>
-      <c r="N18" s="70">
+      <c r="N18" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5190,7 +5213,7 @@
       <c r="B19" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="102" t="s">
+      <c r="C19" s="93" t="s">
         <v>92</v>
       </c>
       <c r="D19" s="19">
@@ -5206,25 +5229,25 @@
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="H19" s="70" t="s">
+      <c r="H19" s="61" t="s">
         <v>91</v>
       </c>
-      <c r="I19" s="70" t="s">
+      <c r="I19" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="J19" s="103" t="s">
+      <c r="J19" s="94" t="s">
         <v>92</v>
       </c>
-      <c r="K19" s="70">
+      <c r="K19" s="61">
         <v>1200</v>
       </c>
-      <c r="L19" s="70">
+      <c r="L19" s="61">
         <v>0</v>
       </c>
-      <c r="M19" s="70">
+      <c r="M19" s="61">
         <v>3</v>
       </c>
-      <c r="N19" s="70">
+      <c r="N19" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5236,7 +5259,7 @@
       <c r="B20" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="104" t="s">
+      <c r="C20" s="95" t="s">
         <v>94</v>
       </c>
       <c r="D20" s="19">
@@ -5252,25 +5275,25 @@
         <f t="shared" si="0"/>
         <v>4000</v>
       </c>
-      <c r="H20" s="70" t="s">
+      <c r="H20" s="61" t="s">
         <v>93</v>
       </c>
-      <c r="I20" s="70" t="s">
+      <c r="I20" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="J20" s="105" t="s">
+      <c r="J20" s="96" t="s">
         <v>94</v>
       </c>
-      <c r="K20" s="70">
+      <c r="K20" s="61">
         <v>1200</v>
       </c>
-      <c r="L20" s="70">
+      <c r="L20" s="61">
         <v>0</v>
       </c>
-      <c r="M20" s="70">
+      <c r="M20" s="61">
         <v>4</v>
       </c>
-      <c r="N20" s="70">
+      <c r="N20" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5282,7 +5305,7 @@
       <c r="B21" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="106" t="s">
+      <c r="C21" s="97" t="s">
         <v>96</v>
       </c>
       <c r="D21" s="19">
@@ -5298,25 +5321,25 @@
         <f t="shared" si="0"/>
         <v>4000</v>
       </c>
-      <c r="H21" s="70" t="s">
+      <c r="H21" s="61" t="s">
         <v>95</v>
       </c>
-      <c r="I21" s="70" t="s">
+      <c r="I21" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="J21" s="107" t="s">
+      <c r="J21" s="98" t="s">
         <v>96</v>
       </c>
-      <c r="K21" s="70">
+      <c r="K21" s="61">
         <v>1200</v>
       </c>
-      <c r="L21" s="70">
+      <c r="L21" s="61">
         <v>0</v>
       </c>
-      <c r="M21" s="70">
+      <c r="M21" s="61">
         <v>4</v>
       </c>
-      <c r="N21" s="70">
+      <c r="N21" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5328,7 +5351,7 @@
       <c r="B22" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="108" t="s">
+      <c r="C22" s="99" t="s">
         <v>98</v>
       </c>
       <c r="D22" s="19">
@@ -5344,25 +5367,25 @@
         <f t="shared" si="0"/>
         <v>5000</v>
       </c>
-      <c r="H22" s="70" t="s">
+      <c r="H22" s="61" t="s">
         <v>97</v>
       </c>
-      <c r="I22" s="70" t="s">
+      <c r="I22" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="J22" s="109" t="s">
+      <c r="J22" s="100" t="s">
         <v>98</v>
       </c>
-      <c r="K22" s="70">
+      <c r="K22" s="61">
         <v>1200</v>
       </c>
-      <c r="L22" s="70">
+      <c r="L22" s="61">
         <v>0</v>
       </c>
-      <c r="M22" s="70">
+      <c r="M22" s="61">
         <v>5</v>
       </c>
-      <c r="N22" s="70">
+      <c r="N22" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5374,7 +5397,7 @@
       <c r="B23" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="110" t="s">
+      <c r="C23" s="101" t="s">
         <v>100</v>
       </c>
       <c r="D23" s="19">
@@ -5390,50 +5413,52 @@
         <f t="shared" si="0"/>
         <v>7000</v>
       </c>
-      <c r="H23" s="70" t="s">
+      <c r="H23" s="61" t="s">
         <v>99</v>
       </c>
-      <c r="I23" s="70" t="s">
+      <c r="I23" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="J23" s="111" t="s">
+      <c r="J23" s="102" t="s">
         <v>100</v>
       </c>
-      <c r="K23" s="70">
+      <c r="K23" s="61">
         <v>1200</v>
       </c>
-      <c r="L23" s="70">
+      <c r="L23" s="61">
         <v>0</v>
       </c>
-      <c r="M23" s="70">
+      <c r="M23" s="61">
         <v>7</v>
       </c>
-      <c r="N23" s="70">
+      <c r="N23" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:14">
-      <c r="A24" s="112"/>
-      <c r="B24" s="112"/>
-      <c r="C24" s="112"/>
-      <c r="D24" s="112"/>
-      <c r="E24" s="112"/>
-      <c r="F24" s="112">
+      <c r="A24" s="103" t="s">
+        <v>333</v>
+      </c>
+      <c r="B24" s="103"/>
+      <c r="C24" s="103"/>
+      <c r="D24" s="103"/>
+      <c r="E24" s="103"/>
+      <c r="F24" s="103">
         <f>SUM(F3:F23)</f>
         <v>127</v>
       </c>
-      <c r="G24" s="112">
+      <c r="G24" s="103">
         <f>SUM(G3:G23)</f>
         <v>127000</v>
       </c>
-      <c r="H24" s="112"/>
-      <c r="I24" s="112"/>
-      <c r="J24" s="112"/>
-      <c r="K24" s="112"/>
-      <c r="L24" s="112"/>
-      <c r="M24" s="112"/>
-      <c r="N24" s="112"/>
+      <c r="H24" s="103"/>
+      <c r="I24" s="103"/>
+      <c r="J24" s="103"/>
+      <c r="K24" s="103"/>
+      <c r="L24" s="103"/>
+      <c r="M24" s="103"/>
+      <c r="N24" s="103"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5456,110 +5481,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="34">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="103" t="s">
         <v>331</v>
       </c>
-      <c r="B1" s="112" t="s">
+      <c r="B1" s="103" t="s">
         <v>328</v>
       </c>
-      <c r="C1" s="113" t="s">
+      <c r="C1" s="104" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="114" t="s">
+      <c r="D1" s="105" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="112" t="s">
+      <c r="A2" s="103" t="s">
         <v>327</v>
       </c>
-      <c r="B2" s="112">
+      <c r="B2" s="103">
         <v>1</v>
       </c>
-      <c r="C2" s="112">
+      <c r="C2" s="103">
         <v>200</v>
       </c>
-      <c r="D2" s="112">
+      <c r="D2" s="103">
         <f>C2*B2</f>
         <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="112" t="s">
+      <c r="A3" s="103" t="s">
         <v>326</v>
       </c>
-      <c r="B3" s="112">
+      <c r="B3" s="103">
         <v>7</v>
       </c>
-      <c r="C3" s="112">
+      <c r="C3" s="103">
         <v>200</v>
       </c>
-      <c r="D3" s="112">
+      <c r="D3" s="103">
         <f t="shared" ref="D3:D7" si="0">C3*B3</f>
         <v>1400</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="112" t="s">
+      <c r="A4" s="103" t="s">
         <v>314</v>
       </c>
-      <c r="B4" s="112">
+      <c r="B4" s="103">
         <v>5</v>
       </c>
-      <c r="C4" s="112">
+      <c r="C4" s="103">
         <v>200</v>
       </c>
-      <c r="D4" s="112">
+      <c r="D4" s="103">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="112" t="s">
+      <c r="A5" s="103" t="s">
         <v>330</v>
       </c>
-      <c r="B5" s="112">
+      <c r="B5" s="103">
         <v>3</v>
       </c>
-      <c r="C5" s="112">
+      <c r="C5" s="103">
         <v>200</v>
       </c>
-      <c r="D5" s="112">
+      <c r="D5" s="103">
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="112" t="s">
+      <c r="A6" s="103" t="s">
         <v>329</v>
       </c>
-      <c r="B6" s="112">
+      <c r="B6" s="103">
         <v>4</v>
       </c>
-      <c r="C6" s="112">
+      <c r="C6" s="103">
         <v>200</v>
       </c>
-      <c r="D6" s="112">
+      <c r="D6" s="103">
         <f t="shared" si="0"/>
         <v>800</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="112" t="s">
+      <c r="A7" s="103" t="s">
         <v>325</v>
       </c>
-      <c r="B7" s="112">
+      <c r="B7" s="103">
         <v>10</v>
       </c>
-      <c r="C7" s="112">
+      <c r="C7" s="103">
         <v>200</v>
       </c>
-      <c r="D7" s="112">
+      <c r="D7" s="103">
         <f t="shared" si="0"/>
         <v>2000</v>
       </c>
     </row>
     <row r="8" spans="1:4">
+      <c r="A8" s="106" t="s">
+        <v>333</v>
+      </c>
       <c r="B8">
         <f>SUM(B2:B7)</f>
         <v>30</v>
@@ -5596,7 +5624,7 @@
       </c>
     </row>
     <row r="2" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="114" t="s">
         <v>102</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -5604,139 +5632,139 @@
       </c>
     </row>
     <row r="3" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A3" s="63"/>
+      <c r="A3" s="115"/>
       <c r="B3" s="1" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A4" s="63"/>
+      <c r="A4" s="115"/>
       <c r="B4" s="1" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A5" s="63"/>
+      <c r="A5" s="115"/>
       <c r="B5" s="1" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A6" s="63"/>
+      <c r="A6" s="115"/>
       <c r="B6" s="1" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A7" s="63"/>
+      <c r="A7" s="115"/>
       <c r="B7" s="1" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A8" s="63"/>
+      <c r="A8" s="115"/>
       <c r="B8" s="1" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A9" s="63"/>
+      <c r="A9" s="115"/>
       <c r="B9" s="1" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A10" s="63"/>
+      <c r="A10" s="115"/>
       <c r="B10" s="1" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A11" s="63"/>
+      <c r="A11" s="115"/>
       <c r="B11" s="1" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A12" s="63"/>
+      <c r="A12" s="115"/>
       <c r="B12" s="1" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A13" s="63"/>
+      <c r="A13" s="115"/>
       <c r="B13" s="1" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A14" s="63"/>
+      <c r="A14" s="115"/>
       <c r="B14" s="1" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A15" s="63"/>
+      <c r="A15" s="115"/>
       <c r="B15" s="1" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A16" s="63"/>
+      <c r="A16" s="115"/>
       <c r="B16" s="1" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A17" s="63"/>
+      <c r="A17" s="115"/>
       <c r="B17" s="1" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A18" s="63"/>
+      <c r="A18" s="115"/>
       <c r="B18" s="1" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A19" s="63"/>
+      <c r="A19" s="115"/>
       <c r="B19" s="1" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A20" s="63"/>
+      <c r="A20" s="115"/>
       <c r="B20" s="1" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A21" s="63"/>
+      <c r="A21" s="115"/>
       <c r="B21" s="1" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A22" s="63"/>
+      <c r="A22" s="115"/>
       <c r="B22" s="1" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A23" s="63"/>
+      <c r="A23" s="115"/>
       <c r="B23" s="1" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A24" s="63"/>
+      <c r="A24" s="115"/>
       <c r="B24" s="1" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A25" s="62" t="s">
+      <c r="A25" s="114" t="s">
         <v>126</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -5744,49 +5772,49 @@
       </c>
     </row>
     <row r="26" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A26" s="63"/>
+      <c r="A26" s="115"/>
       <c r="B26" s="1" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A27" s="63"/>
+      <c r="A27" s="115"/>
       <c r="B27" s="1" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A28" s="63"/>
+      <c r="A28" s="115"/>
       <c r="B28" s="1" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A29" s="63"/>
+      <c r="A29" s="115"/>
       <c r="B29" s="1" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A30" s="63"/>
+      <c r="A30" s="115"/>
       <c r="B30" s="1" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A31" s="63"/>
+      <c r="A31" s="115"/>
       <c r="B31" s="1" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A32" s="63"/>
+      <c r="A32" s="115"/>
       <c r="B32" s="1" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A33" s="62" t="s">
+      <c r="A33" s="114" t="s">
         <v>135</v>
       </c>
       <c r="B33" s="1" t="s">
@@ -5794,91 +5822,91 @@
       </c>
     </row>
     <row r="34" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A34" s="63"/>
+      <c r="A34" s="115"/>
       <c r="B34" s="1" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A35" s="63"/>
+      <c r="A35" s="115"/>
       <c r="B35" s="1" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A36" s="63"/>
+      <c r="A36" s="115"/>
       <c r="B36" s="1" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A37" s="63"/>
+      <c r="A37" s="115"/>
       <c r="B37" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A38" s="63"/>
+      <c r="A38" s="115"/>
       <c r="B38" s="1" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A39" s="63"/>
+      <c r="A39" s="115"/>
       <c r="B39" s="1" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A40" s="63"/>
+      <c r="A40" s="115"/>
       <c r="B40" s="1" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A41" s="63"/>
+      <c r="A41" s="115"/>
       <c r="B41" s="1" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A42" s="63"/>
+      <c r="A42" s="115"/>
       <c r="B42" s="1" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A43" s="63"/>
+      <c r="A43" s="115"/>
       <c r="B43" s="1" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A44" s="63"/>
+      <c r="A44" s="115"/>
       <c r="B44" s="1" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A45" s="63"/>
+      <c r="A45" s="115"/>
       <c r="B45" s="1" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A46" s="63"/>
+      <c r="A46" s="115"/>
       <c r="B46" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A47" s="63"/>
+      <c r="A47" s="115"/>
       <c r="B47" s="1" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A48" s="62" t="s">
+      <c r="A48" s="114" t="s">
         <v>151</v>
       </c>
       <c r="B48" s="1" t="s">
@@ -5886,43 +5914,43 @@
       </c>
     </row>
     <row r="49" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A49" s="63"/>
+      <c r="A49" s="115"/>
       <c r="B49" s="1" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A50" s="63"/>
+      <c r="A50" s="115"/>
       <c r="B50" s="1" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A51" s="63"/>
+      <c r="A51" s="115"/>
       <c r="B51" s="1" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A52" s="63"/>
+      <c r="A52" s="115"/>
       <c r="B52" s="1" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A53" s="63"/>
+      <c r="A53" s="115"/>
       <c r="B53" s="1" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A54" s="63"/>
+      <c r="A54" s="115"/>
       <c r="B54" s="1" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A55" s="62" t="s">
+      <c r="A55" s="114" t="s">
         <v>159</v>
       </c>
       <c r="B55" s="1" t="s">
@@ -5930,73 +5958,73 @@
       </c>
     </row>
     <row r="56" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A56" s="63"/>
+      <c r="A56" s="115"/>
       <c r="B56" s="1" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A57" s="63"/>
+      <c r="A57" s="115"/>
       <c r="B57" s="1" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A58" s="63"/>
+      <c r="A58" s="115"/>
       <c r="B58" s="1" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A59" s="63"/>
+      <c r="A59" s="115"/>
       <c r="B59" s="1" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A60" s="63"/>
+      <c r="A60" s="115"/>
       <c r="B60" s="1" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="61" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A61" s="63"/>
+      <c r="A61" s="115"/>
       <c r="B61" s="1" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="62" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A62" s="63"/>
+      <c r="A62" s="115"/>
       <c r="B62" s="1" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="63" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A63" s="63"/>
+      <c r="A63" s="115"/>
       <c r="B63" s="1" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="64" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A64" s="63"/>
+      <c r="A64" s="115"/>
       <c r="B64" s="1" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="65" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A65" s="63"/>
+      <c r="A65" s="115"/>
       <c r="B65" s="1" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A66" s="63"/>
+      <c r="A66" s="115"/>
       <c r="B66" s="1" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="67" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A67" s="62" t="s">
+      <c r="A67" s="114" t="s">
         <v>172</v>
       </c>
       <c r="B67" s="1" t="s">
@@ -6004,61 +6032,61 @@
       </c>
     </row>
     <row r="68" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A68" s="63"/>
+      <c r="A68" s="115"/>
       <c r="B68" s="1" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="69" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A69" s="63"/>
+      <c r="A69" s="115"/>
       <c r="B69" s="1" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="70" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A70" s="63"/>
+      <c r="A70" s="115"/>
       <c r="B70" s="1" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A71" s="63"/>
+      <c r="A71" s="115"/>
       <c r="B71" s="1" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="72" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A72" s="63"/>
+      <c r="A72" s="115"/>
       <c r="B72" s="1" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="73" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A73" s="63"/>
+      <c r="A73" s="115"/>
       <c r="B73" s="1" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="74" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A74" s="63"/>
+      <c r="A74" s="115"/>
       <c r="B74" s="1" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="75" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A75" s="63"/>
+      <c r="A75" s="115"/>
       <c r="B75" s="1" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="76" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A76" s="63"/>
+      <c r="A76" s="115"/>
       <c r="B76" s="1" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="77" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A77" s="62" t="s">
+      <c r="A77" s="114" t="s">
         <v>182</v>
       </c>
       <c r="B77" s="1" t="s">
@@ -6066,289 +6094,289 @@
       </c>
     </row>
     <row r="78" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A78" s="63"/>
+      <c r="A78" s="115"/>
       <c r="B78" s="1" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="79" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A79" s="63"/>
+      <c r="A79" s="115"/>
       <c r="B79" s="1" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="80" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A80" s="63"/>
+      <c r="A80" s="115"/>
       <c r="B80" s="1" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="81" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A81" s="63"/>
+      <c r="A81" s="115"/>
       <c r="B81" s="1" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="82" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A82" s="63"/>
+      <c r="A82" s="115"/>
       <c r="B82" s="1" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="83" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A83" s="63"/>
+      <c r="A83" s="115"/>
       <c r="B83" s="1" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="84" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A84" s="63"/>
+      <c r="A84" s="115"/>
       <c r="B84" s="1" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="85" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A85" s="63"/>
+      <c r="A85" s="115"/>
       <c r="B85" s="1" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="86" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A86" s="63"/>
+      <c r="A86" s="115"/>
       <c r="B86" s="1" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="87" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A87" s="63"/>
+      <c r="A87" s="115"/>
       <c r="B87" s="1" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="88" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A88" s="63"/>
+      <c r="A88" s="115"/>
       <c r="B88" s="1" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="89" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A89" s="63"/>
+      <c r="A89" s="115"/>
       <c r="B89" s="1" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="90" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A90" s="63"/>
+      <c r="A90" s="115"/>
       <c r="B90" s="1" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="91" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A91" s="63"/>
+      <c r="A91" s="115"/>
       <c r="B91" s="1" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="92" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A92" s="63"/>
+      <c r="A92" s="115"/>
       <c r="B92" s="1" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="93" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A93" s="63"/>
+      <c r="A93" s="115"/>
       <c r="B93" s="1" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="94" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A94" s="63"/>
+      <c r="A94" s="115"/>
       <c r="B94" s="1" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="95" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A95" s="63"/>
+      <c r="A95" s="115"/>
       <c r="B95" s="1" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="96" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A96" s="63"/>
+      <c r="A96" s="115"/>
       <c r="B96" s="1" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="97" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A97" s="63"/>
+      <c r="A97" s="115"/>
       <c r="B97" s="1" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="98" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A98" s="63"/>
+      <c r="A98" s="115"/>
       <c r="B98" s="1" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="99" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A99" s="63"/>
+      <c r="A99" s="115"/>
       <c r="B99" s="1" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="100" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A100" s="63"/>
+      <c r="A100" s="115"/>
       <c r="B100" s="1" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="101" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A101" s="63"/>
+      <c r="A101" s="115"/>
       <c r="B101" s="1" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="102" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A102" s="63"/>
+      <c r="A102" s="115"/>
       <c r="B102" s="1" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="103" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A103" s="63"/>
+      <c r="A103" s="115"/>
       <c r="B103" s="1" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="104" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A104" s="63"/>
+      <c r="A104" s="115"/>
       <c r="B104" s="1" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="105" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A105" s="63"/>
+      <c r="A105" s="115"/>
       <c r="B105" s="1" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="106" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A106" s="63"/>
+      <c r="A106" s="115"/>
       <c r="B106" s="1" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="107" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A107" s="63"/>
+      <c r="A107" s="115"/>
       <c r="B107" s="1" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="108" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A108" s="63"/>
+      <c r="A108" s="115"/>
       <c r="B108" s="1" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="109" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A109" s="63"/>
+      <c r="A109" s="115"/>
       <c r="B109" s="1" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="110" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A110" s="63"/>
+      <c r="A110" s="115"/>
       <c r="B110" s="1" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="111" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A111" s="63"/>
+      <c r="A111" s="115"/>
       <c r="B111" s="1" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="112" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A112" s="63"/>
+      <c r="A112" s="115"/>
       <c r="B112" s="1" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="113" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A113" s="63"/>
+      <c r="A113" s="115"/>
       <c r="B113" s="1" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="114" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A114" s="63"/>
+      <c r="A114" s="115"/>
       <c r="B114" s="1" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="115" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A115" s="63"/>
+      <c r="A115" s="115"/>
       <c r="B115" s="1" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="116" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A116" s="63"/>
+      <c r="A116" s="115"/>
       <c r="B116" s="1" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="117" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A117" s="63"/>
+      <c r="A117" s="115"/>
       <c r="B117" s="1" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="118" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A118" s="63"/>
+      <c r="A118" s="115"/>
       <c r="B118" s="1" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="119" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A119" s="63"/>
+      <c r="A119" s="115"/>
       <c r="B119" s="1" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="120" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A120" s="63"/>
+      <c r="A120" s="115"/>
       <c r="B120" s="1" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="121" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A121" s="63"/>
+      <c r="A121" s="115"/>
       <c r="B121" s="1" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="122" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A122" s="63"/>
+      <c r="A122" s="115"/>
       <c r="B122" s="1" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="123" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A123" s="63"/>
+      <c r="A123" s="115"/>
       <c r="B123" s="1" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="124" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A124" s="63"/>
+      <c r="A124" s="115"/>
       <c r="B124" s="1" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="125" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A125" s="62" t="s">
+      <c r="A125" s="114" t="s">
         <v>230</v>
       </c>
       <c r="B125" s="1" t="s">
@@ -6356,55 +6384,55 @@
       </c>
     </row>
     <row r="126" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A126" s="63"/>
+      <c r="A126" s="115"/>
       <c r="B126" s="1" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="127" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A127" s="63"/>
+      <c r="A127" s="115"/>
       <c r="B127" s="1" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="128" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A128" s="63"/>
+      <c r="A128" s="115"/>
       <c r="B128" s="1" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="129" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A129" s="63"/>
+      <c r="A129" s="115"/>
       <c r="B129" s="1" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="130" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A130" s="63"/>
+      <c r="A130" s="115"/>
       <c r="B130" s="1" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="131" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A131" s="63"/>
+      <c r="A131" s="115"/>
       <c r="B131" s="1" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="132" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A132" s="63"/>
+      <c r="A132" s="115"/>
       <c r="B132" s="1" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="133" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A133" s="63"/>
+      <c r="A133" s="115"/>
       <c r="B133" s="1" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="134" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A134" s="62" t="s">
+      <c r="A134" s="114" t="s">
         <v>240</v>
       </c>
       <c r="B134" s="1" t="s">
@@ -6412,37 +6440,37 @@
       </c>
     </row>
     <row r="135" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A135" s="63"/>
+      <c r="A135" s="115"/>
       <c r="B135" s="1" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="136" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A136" s="63"/>
+      <c r="A136" s="115"/>
       <c r="B136" s="1" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="137" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A137" s="63"/>
+      <c r="A137" s="115"/>
       <c r="B137" s="1" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="138" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A138" s="63"/>
+      <c r="A138" s="115"/>
       <c r="B138" s="1" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="139" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A139" s="63"/>
+      <c r="A139" s="115"/>
       <c r="B139" s="1" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="140" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A140" s="62" t="s">
+      <c r="A140" s="114" t="s">
         <v>247</v>
       </c>
       <c r="B140" s="1" t="s">
@@ -6450,109 +6478,109 @@
       </c>
     </row>
     <row r="141" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A141" s="63"/>
+      <c r="A141" s="115"/>
       <c r="B141" s="1" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="142" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A142" s="63"/>
+      <c r="A142" s="115"/>
       <c r="B142" s="1" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="143" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A143" s="63"/>
+      <c r="A143" s="115"/>
       <c r="B143" s="1" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="144" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A144" s="63"/>
+      <c r="A144" s="115"/>
       <c r="B144" s="1" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="145" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A145" s="63"/>
+      <c r="A145" s="115"/>
       <c r="B145" s="1" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="146" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A146" s="63"/>
+      <c r="A146" s="115"/>
       <c r="B146" s="1" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="147" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A147" s="63"/>
+      <c r="A147" s="115"/>
       <c r="B147" s="1" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="148" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A148" s="63"/>
+      <c r="A148" s="115"/>
       <c r="B148" s="1" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="149" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A149" s="63"/>
+      <c r="A149" s="115"/>
       <c r="B149" s="1" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="150" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A150" s="63"/>
+      <c r="A150" s="115"/>
       <c r="B150" s="1" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="151" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A151" s="63"/>
+      <c r="A151" s="115"/>
       <c r="B151" s="1" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="152" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A152" s="63"/>
+      <c r="A152" s="115"/>
       <c r="B152" s="1" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="153" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A153" s="63"/>
+      <c r="A153" s="115"/>
       <c r="B153" s="1" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="154" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A154" s="63"/>
+      <c r="A154" s="115"/>
       <c r="B154" s="1" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="155" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A155" s="63"/>
+      <c r="A155" s="115"/>
       <c r="B155" s="1" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="156" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A156" s="63"/>
+      <c r="A156" s="115"/>
       <c r="B156" s="1" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="157" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A157" s="63"/>
+      <c r="A157" s="115"/>
       <c r="B157" s="1" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="158" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A158" s="62" t="s">
+      <c r="A158" s="114" t="s">
         <v>266</v>
       </c>
       <c r="B158" s="1" t="s">
@@ -6560,85 +6588,85 @@
       </c>
     </row>
     <row r="159" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A159" s="63"/>
+      <c r="A159" s="115"/>
       <c r="B159" s="1" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="160" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A160" s="63"/>
+      <c r="A160" s="115"/>
       <c r="B160" s="1" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="161" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A161" s="63"/>
+      <c r="A161" s="115"/>
       <c r="B161" s="1" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="162" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A162" s="63"/>
+      <c r="A162" s="115"/>
       <c r="B162" s="1" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="163" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A163" s="63"/>
+      <c r="A163" s="115"/>
       <c r="B163" s="1" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="164" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A164" s="63"/>
+      <c r="A164" s="115"/>
       <c r="B164" s="1" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="165" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A165" s="63"/>
+      <c r="A165" s="115"/>
       <c r="B165" s="1" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="166" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A166" s="63"/>
+      <c r="A166" s="115"/>
       <c r="B166" s="1" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="167" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A167" s="63"/>
+      <c r="A167" s="115"/>
       <c r="B167" s="1" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="168" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A168" s="63"/>
+      <c r="A168" s="115"/>
       <c r="B168" s="1" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="169" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A169" s="63"/>
+      <c r="A169" s="115"/>
       <c r="B169" s="1" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="170" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A170" s="63"/>
+      <c r="A170" s="115"/>
       <c r="B170" s="1" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="171" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A171" s="63"/>
+      <c r="A171" s="115"/>
       <c r="B171" s="1" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="172" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A172" s="62" t="s">
+      <c r="A172" s="114" t="s">
         <v>281</v>
       </c>
       <c r="B172" s="1" t="s">
@@ -6646,43 +6674,43 @@
       </c>
     </row>
     <row r="173" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A173" s="63"/>
+      <c r="A173" s="115"/>
       <c r="B173" s="1" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="174" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A174" s="63"/>
+      <c r="A174" s="115"/>
       <c r="B174" s="1" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="175" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A175" s="63"/>
+      <c r="A175" s="115"/>
       <c r="B175" s="1" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="176" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A176" s="63"/>
+      <c r="A176" s="115"/>
       <c r="B176" s="1" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="177" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A177" s="63"/>
+      <c r="A177" s="115"/>
       <c r="B177" s="1" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="178" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A178" s="63"/>
+      <c r="A178" s="115"/>
       <c r="B178" s="1" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="179" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A179" s="62" t="s">
+      <c r="A179" s="114" t="s">
         <v>289</v>
       </c>
       <c r="B179" s="1" t="s">
@@ -6690,31 +6718,31 @@
       </c>
     </row>
     <row r="180" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A180" s="63"/>
+      <c r="A180" s="115"/>
       <c r="B180" s="1" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="181" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A181" s="63"/>
+      <c r="A181" s="115"/>
       <c r="B181" s="1" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="182" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A182" s="63"/>
+      <c r="A182" s="115"/>
       <c r="B182" s="1" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="183" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A183" s="63"/>
+      <c r="A183" s="115"/>
       <c r="B183" s="1" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="184" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A184" s="62" t="s">
+      <c r="A184" s="114" t="s">
         <v>295</v>
       </c>
       <c r="B184" s="1" t="s">
@@ -6722,31 +6750,31 @@
       </c>
     </row>
     <row r="185" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A185" s="63"/>
+      <c r="A185" s="115"/>
       <c r="B185" s="1" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="186" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A186" s="63"/>
+      <c r="A186" s="115"/>
       <c r="B186" s="1" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="187" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A187" s="63"/>
+      <c r="A187" s="115"/>
       <c r="B187" s="1" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="188" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A188" s="63"/>
+      <c r="A188" s="115"/>
       <c r="B188" s="1" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="189" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A189" s="62" t="s">
+      <c r="A189" s="114" t="s">
         <v>86</v>
       </c>
       <c r="B189" s="1" t="s">
@@ -6754,19 +6782,19 @@
       </c>
     </row>
     <row r="190" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A190" s="63"/>
+      <c r="A190" s="115"/>
       <c r="B190" s="1" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="191" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A191" s="63"/>
+      <c r="A191" s="115"/>
       <c r="B191" s="1" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="192" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A192" s="62" t="s">
+      <c r="A192" s="114" t="s">
         <v>82</v>
       </c>
       <c r="B192" s="1" t="s">
@@ -6774,49 +6802,49 @@
       </c>
     </row>
     <row r="193" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A193" s="63"/>
+      <c r="A193" s="115"/>
       <c r="B193" s="1" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="194" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A194" s="63"/>
+      <c r="A194" s="115"/>
       <c r="B194" s="1" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="195" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A195" s="63"/>
+      <c r="A195" s="115"/>
       <c r="B195" s="1" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="196" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A196" s="63"/>
+      <c r="A196" s="115"/>
       <c r="B196" s="1" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="197" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A197" s="63"/>
+      <c r="A197" s="115"/>
       <c r="B197" s="1" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="198" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A198" s="63"/>
+      <c r="A198" s="115"/>
       <c r="B198" s="1" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="199" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A199" s="63"/>
+      <c r="A199" s="115"/>
       <c r="B199" s="1" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="200" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A200" s="63"/>
+      <c r="A200" s="115"/>
       <c r="B200" s="1" t="s">
         <v>312</v>
       </c>

--- a/issues/728-token-budget-estimation/data/敏捷软件开发AI应用需求情况统计.xlsx
+++ b/issues/728-token-budget-estimation/data/敏捷软件开发AI应用需求情况统计.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/suwei/workspace/astra-flow/poc/issues/728-token-budget-estimation/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01ED2F40-AA58-F94C-97A9-35859CF6EFAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC60E625-982B-5D4C-8F89-4042A817061E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" xr2:uid="{752BAC88-3D22-6345-9E5D-6A586CA68B77}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="2" xr2:uid="{752BAC88-3D22-6345-9E5D-6A586CA68B77}"/>
   </bookViews>
   <sheets>
     <sheet name="应用产品" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="335">
   <si>
     <t>序号</t>
   </si>
@@ -1126,6 +1126,10 @@
   </si>
   <si>
     <t>合计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统及零部件</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1791,7 +1795,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2138,6 +2142,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2649,11 +2656,11 @@
         <v>120</v>
       </c>
       <c r="L3" s="15">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M3" s="15">
         <f t="shared" ref="M3:M18" si="0">K3*L3</f>
-        <v>480</v>
+        <v>960</v>
       </c>
       <c r="N3" s="17" t="s">
         <v>19</v>
@@ -2755,11 +2762,11 @@
         <v>120</v>
       </c>
       <c r="L4" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4" s="15">
         <f t="shared" si="0"/>
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="N4" s="22" t="s">
         <v>19</v>
@@ -2861,11 +2868,11 @@
         <v>120</v>
       </c>
       <c r="L5" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M5" s="15">
         <f t="shared" si="0"/>
-        <v>360</v>
+        <v>720</v>
       </c>
       <c r="N5" s="24" t="s">
         <v>19</v>
@@ -2965,11 +2972,11 @@
         <v>120</v>
       </c>
       <c r="L6" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M6" s="15">
         <f t="shared" si="0"/>
-        <v>240</v>
+        <v>480</v>
       </c>
       <c r="N6" s="26" t="s">
         <v>19</v>
@@ -3071,11 +3078,11 @@
         <v>120</v>
       </c>
       <c r="L7" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M7" s="15">
         <f t="shared" si="0"/>
-        <v>360</v>
+        <v>720</v>
       </c>
       <c r="N7" s="28" t="s">
         <v>40</v>
@@ -3173,11 +3180,11 @@
         <v>120</v>
       </c>
       <c r="L8" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M8" s="15">
         <f t="shared" si="0"/>
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="N8" s="31" t="s">
         <v>40</v>
@@ -3279,11 +3286,11 @@
         <v>120</v>
       </c>
       <c r="L9" s="15">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="M9" s="15">
         <f t="shared" si="0"/>
-        <v>1080</v>
+        <v>2160</v>
       </c>
       <c r="N9" s="33" t="s">
         <v>19</v>
@@ -3383,11 +3390,11 @@
         <v>120</v>
       </c>
       <c r="L10" s="15">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M10" s="15">
         <f t="shared" si="0"/>
-        <v>480</v>
+        <v>960</v>
       </c>
       <c r="N10" s="36" t="s">
         <v>53</v>
@@ -3489,11 +3496,11 @@
         <v>120</v>
       </c>
       <c r="L11" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M11" s="15">
         <f t="shared" si="0"/>
-        <v>240</v>
+        <v>480</v>
       </c>
       <c r="N11" s="39" t="s">
         <v>19</v>
@@ -3593,11 +3600,11 @@
         <v>120</v>
       </c>
       <c r="L12" s="15">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M12" s="15">
         <f t="shared" si="0"/>
-        <v>480</v>
+        <v>960</v>
       </c>
       <c r="N12" s="41" t="s">
         <v>64</v>
@@ -3699,11 +3706,11 @@
         <v>120</v>
       </c>
       <c r="L13" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M13" s="15">
         <f t="shared" si="0"/>
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="N13" s="44" t="s">
         <v>19</v>
@@ -3805,11 +3812,11 @@
         <v>120</v>
       </c>
       <c r="L14" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M14" s="15">
         <f t="shared" si="0"/>
-        <v>240</v>
+        <v>480</v>
       </c>
       <c r="N14" s="46" t="s">
         <v>19</v>
@@ -3911,11 +3918,11 @@
         <v>120</v>
       </c>
       <c r="L15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M15" s="15">
         <f t="shared" si="0"/>
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="N15" s="47" t="s">
         <v>19</v>
@@ -4017,11 +4024,11 @@
         <v>120</v>
       </c>
       <c r="L16" s="15">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="M16" s="15">
         <f t="shared" si="0"/>
-        <v>840</v>
+        <v>1680</v>
       </c>
       <c r="N16" s="49" t="s">
         <v>64</v>
@@ -4121,11 +4128,11 @@
         <v>120</v>
       </c>
       <c r="L17" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M17" s="15">
         <f t="shared" si="0"/>
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="N17" s="51" t="s">
         <v>53</v>
@@ -4227,11 +4234,11 @@
         <v>120</v>
       </c>
       <c r="L18" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M18" s="15">
         <f t="shared" si="0"/>
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="N18" s="54" t="s">
         <v>87</v>
@@ -4338,11 +4345,11 @@
       </c>
       <c r="L20">
         <f>SUM(L3:L19)</f>
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="M20">
         <f>SUM(M3:M19)</f>
-        <v>5520</v>
+        <v>11040</v>
       </c>
       <c r="R20">
         <f>SUM(R3:R19)</f>
@@ -5472,7 +5479,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E72B87AF-C8B2-4E49-8B00-49591E23A6A9}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="20.1640625" customWidth="1"/>
@@ -5520,7 +5527,7 @@
         <v>200</v>
       </c>
       <c r="D3" s="103">
-        <f t="shared" ref="D3:D7" si="0">C3*B3</f>
+        <f t="shared" ref="D3:D8" si="0">C3*B3</f>
         <v>1400</v>
       </c>
     </row>
@@ -5586,15 +5593,30 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="106" t="s">
+        <v>334</v>
+      </c>
+      <c r="B8" s="116">
+        <v>146</v>
+      </c>
+      <c r="C8" s="116">
+        <v>200</v>
+      </c>
+      <c r="D8" s="116">
+        <f t="shared" si="0"/>
+        <v>29200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="106" t="s">
         <v>333</v>
       </c>
-      <c r="B8">
-        <f>SUM(B2:B7)</f>
-        <v>30</v>
-      </c>
-      <c r="D8">
-        <f>SUM(D2:D7)</f>
-        <v>6000</v>
+      <c r="B9">
+        <f>SUM(B2:B8)</f>
+        <v>176</v>
+      </c>
+      <c r="D9">
+        <f>SUM(D2:D8)</f>
+        <v>35200</v>
       </c>
     </row>
   </sheetData>
@@ -6851,22 +6873,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A2:A24"/>
+    <mergeCell ref="A25:A32"/>
+    <mergeCell ref="A33:A47"/>
+    <mergeCell ref="A48:A54"/>
+    <mergeCell ref="A55:A66"/>
+    <mergeCell ref="A67:A76"/>
+    <mergeCell ref="A77:A124"/>
+    <mergeCell ref="A125:A133"/>
+    <mergeCell ref="A134:A139"/>
+    <mergeCell ref="A140:A157"/>
     <mergeCell ref="A192:A200"/>
     <mergeCell ref="A158:A171"/>
     <mergeCell ref="A172:A178"/>
     <mergeCell ref="A179:A183"/>
     <mergeCell ref="A184:A188"/>
     <mergeCell ref="A189:A191"/>
-    <mergeCell ref="A67:A76"/>
-    <mergeCell ref="A77:A124"/>
-    <mergeCell ref="A125:A133"/>
-    <mergeCell ref="A134:A139"/>
-    <mergeCell ref="A140:A157"/>
-    <mergeCell ref="A2:A24"/>
-    <mergeCell ref="A25:A32"/>
-    <mergeCell ref="A33:A47"/>
-    <mergeCell ref="A48:A54"/>
-    <mergeCell ref="A55:A66"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/issues/728-token-budget-estimation/data/敏捷软件开发AI应用需求情况统计.xlsx
+++ b/issues/728-token-budget-estimation/data/敏捷软件开发AI应用需求情况统计.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/suwei/workspace/astra-flow/poc/issues/728-token-budget-estimation/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC60E625-982B-5D4C-8F89-4042A817061E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C69CC285-D32C-C84A-92E3-15C21A4EEE19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="2" xr2:uid="{752BAC88-3D22-6345-9E5D-6A586CA68B77}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="68800" windowHeight="28800" activeTab="1" xr2:uid="{752BAC88-3D22-6345-9E5D-6A586CA68B77}"/>
   </bookViews>
   <sheets>
     <sheet name="应用产品" sheetId="1" r:id="rId1"/>
     <sheet name="基础软件" sheetId="3" r:id="rId2"/>
     <sheet name="其他业务" sheetId="4" r:id="rId3"/>
-    <sheet name="产品功能列表" sheetId="2" state="hidden" r:id="rId4"/>
+    <sheet name="在岗人员（2026年底）" sheetId="5" r:id="rId4"/>
+    <sheet name="产品功能列表" sheetId="2" state="hidden" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="345">
   <si>
     <t>序号</t>
   </si>
@@ -80,9 +81,6 @@
   </si>
   <si>
     <t>系统模块</t>
-  </si>
-  <si>
-    <t>是否AI分析</t>
   </si>
   <si>
     <t>是否AI</t>
@@ -114,9 +112,6 @@
     <t>Android Framework</t>
   </si>
   <si>
-    <t>是</t>
-  </si>
-  <si>
     <t>deepseek v4 pro
 Qwen3.7 Max
 GLM5.2</t>
@@ -1046,10 +1041,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>综合业务</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>PRD及HMI成图</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1088,15 +1079,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>日志分析</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>软件研发管控</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>人力</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1129,7 +1112,56 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>系统及零部件</t>
+    <t>在岗人数</t>
+  </si>
+  <si>
+    <t>预计年末到岗</t>
+  </si>
+  <si>
+    <t>车机应用软件开发</t>
+  </si>
+  <si>
+    <t>综合管理</t>
+  </si>
+  <si>
+    <t>座舱产品设计</t>
+  </si>
+  <si>
+    <t>车机软件测试</t>
+  </si>
+  <si>
+    <t>车机基础软件开发</t>
+  </si>
+  <si>
+    <t>车机云开发</t>
+  </si>
+  <si>
+    <t>财务管理</t>
+  </si>
+  <si>
+    <t>质量与运营</t>
+  </si>
+  <si>
+    <t>硬件设计</t>
+  </si>
+  <si>
+    <t>业务领域</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>调研表各场景总人数合计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>硬件设计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>综合管理（人力+行政）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财务管理</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1137,7 +1169,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="91">
+  <fonts count="68">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1229,490 +1261,350 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="10"/>
       <name val="等线"/>
       <family val="4"/>
       <charset val="134"/>
     </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1726,11 +1618,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFAE5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE8F2FE"/>
       </patternFill>
     </fill>
@@ -1740,7 +1627,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1789,13 +1676,41 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1811,19 +1726,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1832,277 +1747,202 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="29" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="23" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="27" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="34" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="53" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="57" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="87" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="59" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
@@ -2117,13 +1957,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2132,10 +1972,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2144,7 +1981,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2472,50 +2321,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" s="3" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="84" t="s">
+        <v>311</v>
+      </c>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="82" t="s">
+        <v>312</v>
+      </c>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
+      <c r="M1" s="83"/>
+      <c r="N1" s="87" t="s">
         <v>313</v>
       </c>
-      <c r="B1" s="110"/>
-      <c r="C1" s="110"/>
-      <c r="D1" s="110"/>
-      <c r="E1" s="110"/>
-      <c r="F1" s="107" t="s">
-        <v>315</v>
-      </c>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="112" t="s">
+      <c r="O1" s="83"/>
+      <c r="P1" s="83"/>
+      <c r="Q1" s="83"/>
+      <c r="R1" s="83"/>
+      <c r="S1" s="83"/>
+      <c r="T1" s="83"/>
+      <c r="U1" s="86" t="s">
+        <v>314</v>
+      </c>
+      <c r="V1" s="83"/>
+      <c r="W1" s="83"/>
+      <c r="X1" s="83"/>
+      <c r="Y1" s="83"/>
+      <c r="Z1" s="83"/>
+      <c r="AA1" s="83"/>
+      <c r="AB1" s="82" t="s">
         <v>316</v>
       </c>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="111" t="s">
-        <v>317</v>
-      </c>
-      <c r="V1" s="108"/>
-      <c r="W1" s="108"/>
-      <c r="X1" s="108"/>
-      <c r="Y1" s="108"/>
-      <c r="Z1" s="108"/>
-      <c r="AA1" s="108"/>
-      <c r="AB1" s="107" t="s">
-        <v>319</v>
-      </c>
-      <c r="AC1" s="108"/>
-      <c r="AD1" s="108"/>
-      <c r="AE1" s="108"/>
-      <c r="AF1" s="108"/>
-      <c r="AG1" s="108"/>
-      <c r="AH1" s="108"/>
+      <c r="AC1" s="83"/>
+      <c r="AD1" s="83"/>
+      <c r="AE1" s="83"/>
+      <c r="AF1" s="83"/>
+      <c r="AG1" s="83"/>
+      <c r="AH1" s="83"/>
     </row>
     <row r="2" spans="1:34" s="3" customFormat="1" ht="41.25" customHeight="1">
       <c r="A2" s="4" t="s">
@@ -2540,13 +2389,13 @@
         <v>6</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>7</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="K2" s="8" t="s">
         <v>8</v>
@@ -2555,7 +2404,7 @@
         <v>9</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="N2" s="6" t="s">
         <v>5</v>
@@ -2567,7 +2416,7 @@
         <v>7</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="R2" s="9" t="s">
         <v>8</v>
@@ -2588,7 +2437,7 @@
         <v>7</v>
       </c>
       <c r="X2" s="7" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="Y2" s="10" t="s">
         <v>8</v>
@@ -2609,7 +2458,7 @@
         <v>7</v>
       </c>
       <c r="AE2" s="5" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="AF2" s="12" t="s">
         <v>8</v>
@@ -2626,7 +2475,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" s="14">
         <v>23</v>
@@ -2638,7 +2487,7 @@
         <v>465</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G3" s="16">
         <v>0.3</v>
@@ -2647,7 +2496,7 @@
         <v>0.8</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J3" s="15">
         <v>100</v>
@@ -2663,13 +2512,13 @@
         <v>960</v>
       </c>
       <c r="N3" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O3" s="18">
         <v>0.3</v>
       </c>
       <c r="P3" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q3" s="19">
         <v>100</v>
@@ -2685,13 +2534,13 @@
         <v>60</v>
       </c>
       <c r="U3" s="20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V3" s="21">
         <v>0.4</v>
       </c>
       <c r="W3" s="20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="X3" s="20">
         <v>240</v>
@@ -2700,31 +2549,31 @@
         <v>65</v>
       </c>
       <c r="Z3" s="20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA3" s="20">
         <f t="shared" ref="AA3:AA18" si="2">Y3*Z3</f>
-        <v>520</v>
+        <v>650</v>
       </c>
       <c r="AB3" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC3" s="16">
         <v>0.5</v>
       </c>
       <c r="AD3" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE3" s="15"/>
       <c r="AF3" s="15">
         <v>200</v>
       </c>
       <c r="AG3" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH3" s="15">
         <f t="shared" ref="AH3:AH18" si="3">AF3*AG3</f>
-        <v>400</v>
+        <v>800</v>
       </c>
     </row>
     <row r="4" spans="1:34" ht="41.25" customHeight="1">
@@ -2732,7 +2581,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C4" s="14">
         <v>8</v>
@@ -2744,7 +2593,7 @@
         <v>313</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G4" s="16">
         <v>0.1</v>
@@ -2753,7 +2602,7 @@
         <v>0.8</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J4" s="15">
         <v>100</v>
@@ -2769,13 +2618,13 @@
         <v>240</v>
       </c>
       <c r="N4" s="22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O4" s="18">
         <v>0.4</v>
       </c>
       <c r="P4" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q4" s="19">
         <v>100</v>
@@ -2791,13 +2640,13 @@
         <v>60</v>
       </c>
       <c r="U4" s="20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V4" s="21">
         <v>0.25</v>
       </c>
       <c r="W4" s="23" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="X4" s="20">
         <v>210</v>
@@ -2806,31 +2655,31 @@
         <v>60</v>
       </c>
       <c r="Z4" s="20">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA4" s="20">
         <f t="shared" si="2"/>
-        <v>420</v>
+        <v>540</v>
       </c>
       <c r="AB4" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC4" s="16">
         <v>0.5</v>
       </c>
       <c r="AD4" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE4" s="15"/>
       <c r="AF4" s="15">
         <v>200</v>
       </c>
       <c r="AG4" s="15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AH4" s="15">
         <f t="shared" si="3"/>
-        <v>200</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="5" spans="1:34" ht="41.25" customHeight="1">
@@ -2838,7 +2687,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C5" s="14">
         <v>15</v>
@@ -2850,7 +2699,7 @@
         <v>262</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G5" s="16">
         <v>0.1</v>
@@ -2859,7 +2708,7 @@
         <v>0.8</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J5" s="15">
         <v>100</v>
@@ -2875,13 +2724,13 @@
         <v>720</v>
       </c>
       <c r="N5" s="24" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O5" s="18">
         <v>0.55000000000000004</v>
       </c>
       <c r="P5" s="19" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="Q5" s="19">
         <v>120</v>
@@ -2897,13 +2746,13 @@
         <v>0</v>
       </c>
       <c r="U5" s="20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V5" s="21">
         <v>0.6</v>
       </c>
       <c r="W5" s="25" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="X5" s="20"/>
       <c r="Y5" s="20">
@@ -2917,24 +2766,24 @@
         <v>5200</v>
       </c>
       <c r="AB5" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC5" s="16">
         <v>0.7</v>
       </c>
       <c r="AD5" s="15" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="AE5" s="15"/>
       <c r="AF5" s="15">
         <v>200</v>
       </c>
       <c r="AG5" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH5" s="15">
         <f t="shared" si="3"/>
-        <v>400</v>
+        <v>800</v>
       </c>
     </row>
     <row r="6" spans="1:34" ht="41.25" customHeight="1">
@@ -2942,7 +2791,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C6" s="14">
         <v>7</v>
@@ -2954,7 +2803,7 @@
         <v>112</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G6" s="16">
         <v>0.1</v>
@@ -2963,7 +2812,7 @@
         <v>0.8</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J6" s="15">
         <v>100</v>
@@ -2979,13 +2828,13 @@
         <v>480</v>
       </c>
       <c r="N6" s="26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O6" s="18">
         <v>0.3</v>
       </c>
       <c r="P6" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q6" s="19">
         <v>100</v>
@@ -3001,13 +2850,13 @@
         <v>60</v>
       </c>
       <c r="U6" s="20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V6" s="21">
         <v>0.25</v>
       </c>
       <c r="W6" s="27" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="X6" s="20">
         <v>60</v>
@@ -3016,31 +2865,31 @@
         <v>60</v>
       </c>
       <c r="Z6" s="20">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AA6" s="20">
         <f t="shared" si="2"/>
-        <v>120</v>
+        <v>360</v>
       </c>
       <c r="AB6" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC6" s="16">
         <v>0.5</v>
       </c>
       <c r="AD6" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE6" s="15"/>
       <c r="AF6" s="15">
         <v>200</v>
       </c>
       <c r="AG6" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AH6" s="15">
         <f t="shared" si="3"/>
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7" spans="1:34" ht="41.25" customHeight="1">
@@ -3048,7 +2897,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C7" s="14">
         <v>12</v>
@@ -3060,7 +2909,7 @@
         <v>190</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G7" s="16">
         <v>0.1</v>
@@ -3069,7 +2918,7 @@
         <v>0.8</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J7" s="15">
         <v>100</v>
@@ -3085,13 +2934,13 @@
         <v>720</v>
       </c>
       <c r="N7" s="28" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O7" s="18">
         <v>0.6</v>
       </c>
       <c r="P7" s="29" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q7" s="19">
         <v>180</v>
@@ -3107,13 +2956,13 @@
         <v>0</v>
       </c>
       <c r="U7" s="20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V7" s="21">
         <v>0.25</v>
       </c>
       <c r="W7" s="30" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="X7" s="20">
         <v>30</v>
@@ -3122,16 +2971,16 @@
         <v>60</v>
       </c>
       <c r="Z7" s="20">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AA7" s="20">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>480</v>
       </c>
       <c r="AB7" s="15"/>
       <c r="AC7" s="15"/>
       <c r="AD7" s="15" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="AE7" s="15"/>
       <c r="AF7" s="15">
@@ -3150,7 +2999,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C8" s="14">
         <v>10</v>
@@ -3162,7 +3011,7 @@
         <v>155</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G8" s="16">
         <v>0.1</v>
@@ -3171,7 +3020,7 @@
         <v>0.8</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J8" s="15">
         <v>100</v>
@@ -3187,13 +3036,13 @@
         <v>240</v>
       </c>
       <c r="N8" s="31" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O8" s="18">
         <v>0.5</v>
       </c>
       <c r="P8" s="32" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q8" s="19">
         <v>120</v>
@@ -3209,13 +3058,13 @@
         <v>0</v>
       </c>
       <c r="U8" s="20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V8" s="21">
         <v>0.3</v>
       </c>
       <c r="W8" s="25" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="X8" s="20">
         <v>40</v>
@@ -3224,31 +3073,31 @@
         <v>210</v>
       </c>
       <c r="Z8" s="20">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AA8" s="20">
         <f t="shared" si="2"/>
-        <v>420</v>
+        <v>1890</v>
       </c>
       <c r="AB8" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC8" s="16">
         <v>0.5</v>
       </c>
       <c r="AD8" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE8" s="15"/>
       <c r="AF8" s="15">
         <v>200</v>
       </c>
       <c r="AG8" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AH8" s="15">
         <f t="shared" si="3"/>
-        <v>200</v>
+        <v>800</v>
       </c>
     </row>
     <row r="9" spans="1:34" ht="41.25" customHeight="1">
@@ -3256,7 +3105,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C9" s="14">
         <v>48</v>
@@ -3268,7 +3117,7 @@
         <v>1049</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G9" s="16">
         <v>0.1</v>
@@ -3277,7 +3126,7 @@
         <v>0.8</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J9" s="15">
         <v>100</v>
@@ -3293,13 +3142,13 @@
         <v>2160</v>
       </c>
       <c r="N9" s="33" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O9" s="18">
         <v>0.3</v>
       </c>
       <c r="P9" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q9" s="19">
         <v>100</v>
@@ -3315,44 +3164,44 @@
         <v>60</v>
       </c>
       <c r="U9" s="20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V9" s="21">
         <v>0.8</v>
       </c>
       <c r="W9" s="34" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="X9" s="20"/>
       <c r="Y9" s="20">
         <v>700</v>
       </c>
       <c r="Z9" s="20">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AA9" s="20">
         <f t="shared" si="2"/>
-        <v>7000</v>
+        <v>9800</v>
       </c>
       <c r="AB9" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC9" s="16">
         <v>0.8</v>
       </c>
       <c r="AD9" s="35" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE9" s="15"/>
       <c r="AF9" s="15">
         <v>200</v>
       </c>
       <c r="AG9" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AH9" s="15">
         <f t="shared" si="3"/>
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="10" spans="1:34" ht="41.25" customHeight="1">
@@ -3360,7 +3209,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C10" s="14">
         <v>9</v>
@@ -3372,7 +3221,7 @@
         <v>290</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G10" s="16">
         <v>0.2</v>
@@ -3381,7 +3230,7 @@
         <v>0.8</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J10" s="15">
         <v>100</v>
@@ -3397,13 +3246,13 @@
         <v>960</v>
       </c>
       <c r="N10" s="36" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="O10" s="18">
         <v>0.6</v>
       </c>
       <c r="P10" s="37" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="Q10" s="19">
         <v>180</v>
@@ -3419,13 +3268,13 @@
         <v>200</v>
       </c>
       <c r="U10" s="20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V10" s="21">
         <v>0.5</v>
       </c>
       <c r="W10" s="38" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="X10" s="20">
         <v>270</v>
@@ -3441,24 +3290,24 @@
         <v>1800</v>
       </c>
       <c r="AB10" s="15" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AC10" s="15">
         <v>0</v>
       </c>
       <c r="AD10" s="15" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="AE10" s="15"/>
       <c r="AF10" s="15">
         <v>200</v>
       </c>
       <c r="AG10" s="15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AH10" s="15">
         <f t="shared" si="3"/>
-        <v>200</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="11" spans="1:34" ht="41.25" customHeight="1">
@@ -3466,7 +3315,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C11" s="14">
         <v>6</v>
@@ -3478,7 +3327,7 @@
         <v>229</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G11" s="16">
         <v>0.1</v>
@@ -3487,7 +3336,7 @@
         <v>0.8</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J11" s="15">
         <v>100</v>
@@ -3503,13 +3352,13 @@
         <v>480</v>
       </c>
       <c r="N11" s="39" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O11" s="18">
         <v>0.3</v>
       </c>
       <c r="P11" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q11" s="19">
         <v>100</v>
@@ -3525,13 +3374,13 @@
         <v>60</v>
       </c>
       <c r="U11" s="20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V11" s="21">
         <v>0.8</v>
       </c>
       <c r="W11" s="40" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="X11" s="20"/>
       <c r="Y11" s="20">
@@ -3545,24 +3394,24 @@
         <v>11200</v>
       </c>
       <c r="AB11" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC11" s="16">
         <v>0.2</v>
       </c>
       <c r="AD11" s="15" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="AE11" s="15"/>
       <c r="AF11" s="15">
         <v>200</v>
       </c>
       <c r="AG11" s="15">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AH11" s="15">
         <f t="shared" si="3"/>
-        <v>400</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="12" spans="1:34" ht="41.25" customHeight="1">
@@ -3570,7 +3419,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C12" s="14">
         <v>18</v>
@@ -3582,7 +3431,7 @@
         <v>586</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G12" s="16">
         <v>0.1</v>
@@ -3591,7 +3440,7 @@
         <v>0.8</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J12" s="15">
         <v>100</v>
@@ -3607,13 +3456,13 @@
         <v>960</v>
       </c>
       <c r="N12" s="41" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="O12" s="18">
         <v>0.3</v>
       </c>
       <c r="P12" s="19" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="Q12" s="19">
         <v>100</v>
@@ -3629,13 +3478,13 @@
         <v>0</v>
       </c>
       <c r="U12" s="25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V12" s="42">
         <v>0.5</v>
       </c>
       <c r="W12" s="43" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="X12" s="25">
         <v>510</v>
@@ -3651,24 +3500,24 @@
         <v>2040</v>
       </c>
       <c r="AB12" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC12" s="16">
         <v>0.5</v>
       </c>
       <c r="AD12" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE12" s="15"/>
       <c r="AF12" s="15">
         <v>200</v>
       </c>
       <c r="AG12" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH12" s="15">
         <f t="shared" si="3"/>
-        <v>400</v>
+        <v>800</v>
       </c>
     </row>
     <row r="13" spans="1:34" ht="41.25" customHeight="1">
@@ -3676,7 +3525,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C13" s="14">
         <v>14</v>
@@ -3688,7 +3537,7 @@
         <v>300</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G13" s="16">
         <v>0.1</v>
@@ -3697,7 +3546,7 @@
         <v>0.8</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J13" s="15">
         <v>100</v>
@@ -3713,13 +3562,13 @@
         <v>240</v>
       </c>
       <c r="N13" s="44" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O13" s="18">
         <v>0.3</v>
       </c>
       <c r="P13" s="19" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Q13" s="19">
         <v>100</v>
@@ -3735,13 +3584,13 @@
         <v>0</v>
       </c>
       <c r="U13" s="25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V13" s="42">
         <v>0.4</v>
       </c>
       <c r="W13" s="45" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="X13" s="25">
         <v>390</v>
@@ -3757,24 +3606,24 @@
         <v>2600</v>
       </c>
       <c r="AB13" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC13" s="16">
         <v>0.5</v>
       </c>
       <c r="AD13" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE13" s="15"/>
       <c r="AF13" s="15">
         <v>200</v>
       </c>
       <c r="AG13" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AH13" s="15">
         <f t="shared" si="3"/>
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="14" spans="1:34" ht="41.25" customHeight="1">
@@ -3782,7 +3631,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C14" s="14">
         <v>7</v>
@@ -3794,7 +3643,7 @@
         <v>112</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G14" s="16">
         <v>0.2</v>
@@ -3803,7 +3652,7 @@
         <v>0.8</v>
       </c>
       <c r="I14" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J14" s="15">
         <v>100</v>
@@ -3819,13 +3668,13 @@
         <v>480</v>
       </c>
       <c r="N14" s="46" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O14" s="18">
         <v>0.3</v>
       </c>
       <c r="P14" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q14" s="19">
         <v>100</v>
@@ -3841,13 +3690,13 @@
         <v>60</v>
       </c>
       <c r="U14" s="20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V14" s="21">
         <v>0.4</v>
       </c>
       <c r="W14" s="25" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="X14" s="20">
         <v>120</v>
@@ -3856,31 +3705,31 @@
         <v>210</v>
       </c>
       <c r="Z14" s="20">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AA14" s="20">
         <f t="shared" si="2"/>
-        <v>840</v>
+        <v>2310</v>
       </c>
       <c r="AB14" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC14" s="16">
         <v>0.5</v>
       </c>
       <c r="AD14" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE14" s="15"/>
       <c r="AF14" s="15">
         <v>200</v>
       </c>
       <c r="AG14" s="15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AH14" s="15">
         <f t="shared" si="3"/>
-        <v>200</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="15" spans="1:34" ht="41.25" customHeight="1">
@@ -3888,7 +3737,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C15" s="14">
         <v>5</v>
@@ -3900,7 +3749,7 @@
         <v>71</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G15" s="16">
         <v>0.1</v>
@@ -3909,7 +3758,7 @@
         <v>0.8</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J15" s="15">
         <v>100</v>
@@ -3925,13 +3774,13 @@
         <v>240</v>
       </c>
       <c r="N15" s="47" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O15" s="18">
         <v>0.3</v>
       </c>
       <c r="P15" s="19" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="Q15" s="19">
         <v>100</v>
@@ -3947,13 +3796,13 @@
         <v>0</v>
       </c>
       <c r="U15" s="20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V15" s="21">
         <v>0.25</v>
       </c>
       <c r="W15" s="48" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="X15" s="20">
         <v>90</v>
@@ -3962,20 +3811,20 @@
         <v>60</v>
       </c>
       <c r="Z15" s="20">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AA15" s="20">
         <f t="shared" si="2"/>
-        <v>180</v>
+        <v>600</v>
       </c>
       <c r="AB15" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC15" s="16">
         <v>0.5</v>
       </c>
       <c r="AD15" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE15" s="15"/>
       <c r="AF15" s="15">
@@ -3994,7 +3843,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C16" s="14">
         <v>5</v>
@@ -4006,7 +3855,7 @@
         <v>382</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G16" s="16">
         <v>0.1</v>
@@ -4015,7 +3864,7 @@
         <v>0.8</v>
       </c>
       <c r="I16" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J16" s="15">
         <v>100</v>
@@ -4031,13 +3880,13 @@
         <v>1680</v>
       </c>
       <c r="N16" s="49" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="O16" s="18">
         <v>0.3</v>
       </c>
       <c r="P16" s="19" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="Q16" s="19">
         <v>100</v>
@@ -4053,44 +3902,44 @@
         <v>0</v>
       </c>
       <c r="U16" s="20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V16" s="21">
         <v>0.8</v>
       </c>
       <c r="W16" s="50" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="X16" s="20"/>
       <c r="Y16" s="20">
         <v>700</v>
       </c>
       <c r="Z16" s="20">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="AA16" s="20">
         <f t="shared" si="2"/>
-        <v>4200</v>
+        <v>10500</v>
       </c>
       <c r="AB16" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC16" s="16">
         <v>0.4</v>
       </c>
       <c r="AD16" s="15" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="AE16" s="15"/>
       <c r="AF16" s="15">
         <v>200</v>
       </c>
       <c r="AG16" s="15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AH16" s="15">
         <f t="shared" si="3"/>
-        <v>200</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="17" spans="1:34" ht="41.25" customHeight="1">
@@ -4098,7 +3947,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C17" s="14">
         <v>9</v>
@@ -4110,7 +3959,7 @@
         <v>196</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G17" s="16">
         <v>0.1</v>
@@ -4119,7 +3968,7 @@
         <v>0.8</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J17" s="15">
         <v>100</v>
@@ -4135,13 +3984,13 @@
         <v>240</v>
       </c>
       <c r="N17" s="51" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="O17" s="18">
         <v>0.6</v>
       </c>
       <c r="P17" s="52" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="Q17" s="19">
         <v>180</v>
@@ -4157,13 +4006,13 @@
         <v>200</v>
       </c>
       <c r="U17" s="20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V17" s="21">
         <v>0.3</v>
       </c>
       <c r="W17" s="53" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="X17" s="20">
         <v>570</v>
@@ -4179,24 +4028,24 @@
         <v>3800</v>
       </c>
       <c r="AB17" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC17" s="16">
         <v>0.5</v>
       </c>
       <c r="AD17" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE17" s="15"/>
       <c r="AF17" s="15">
         <v>200</v>
       </c>
       <c r="AG17" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH17" s="15">
         <f t="shared" si="3"/>
-        <v>200</v>
+        <v>600</v>
       </c>
     </row>
     <row r="18" spans="1:34" ht="41.25" customHeight="1">
@@ -4204,7 +4053,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C18" s="14">
         <v>3</v>
@@ -4216,7 +4065,7 @@
         <v>45</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G18" s="16">
         <v>0.1</v>
@@ -4225,7 +4074,7 @@
         <v>0.8</v>
       </c>
       <c r="I18" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J18" s="15">
         <v>100</v>
@@ -4241,13 +4090,13 @@
         <v>240</v>
       </c>
       <c r="N18" s="54" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O18" s="18">
         <v>0.5</v>
       </c>
       <c r="P18" s="19" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="Q18" s="19">
         <v>180</v>
@@ -4263,33 +4112,33 @@
         <v>0</v>
       </c>
       <c r="U18" s="20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V18" s="21">
         <v>0.8</v>
       </c>
       <c r="W18" s="55" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="X18" s="20"/>
       <c r="Y18" s="25">
         <v>200</v>
       </c>
       <c r="Z18" s="20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA18" s="20">
         <f t="shared" si="2"/>
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="AB18" s="15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AC18" s="15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AD18" s="15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AE18" s="15"/>
       <c r="AF18" s="15">
@@ -4341,7 +4190,7 @@
     </row>
     <row r="20" spans="1:34" ht="41.25" customHeight="1">
       <c r="A20" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="L20">
         <f>SUM(L3:L19)</f>
@@ -4365,19 +4214,19 @@
       </c>
       <c r="Z20">
         <f>SUM(Z3:Z18)</f>
-        <v>152</v>
+        <v>202</v>
       </c>
       <c r="AA20">
         <f>SUM(AA3:AA19)</f>
-        <v>42200</v>
+        <v>55770</v>
       </c>
       <c r="AG20">
         <f>SUM(AG3:AG18)</f>
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="AH20">
         <f>SUM(AH3:AH18)</f>
-        <v>5800</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="21" spans="1:34" ht="41.25" customHeight="1"/>
@@ -4397,95 +4246,58 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A3760BD-E7CA-BC43-AC57-8E6A5D56F59E}">
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="16.83203125" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
     <col min="5" max="5" width="13.33203125" customWidth="1"/>
     <col min="7" max="7" width="19.1640625" customWidth="1"/>
-    <col min="8" max="8" width="13.1640625" customWidth="1"/>
-    <col min="9" max="9" width="10"/>
-    <col min="10" max="10" width="13.6640625" customWidth="1"/>
-    <col min="11" max="11" width="15.33203125" customWidth="1"/>
-    <col min="12" max="12" width="11.5" customWidth="1"/>
-    <col min="13" max="13" width="10"/>
-    <col min="14" max="14" width="19.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="112" t="s">
-        <v>323</v>
-      </c>
-      <c r="B1" s="108"/>
-      <c r="C1" s="108"/>
-      <c r="D1" s="108"/>
-      <c r="E1" s="108"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
-      <c r="H1" s="113" t="s">
-        <v>324</v>
-      </c>
-      <c r="I1" s="108"/>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-    </row>
-    <row r="2" spans="1:14" ht="28">
+    <row r="1" spans="1:7">
+      <c r="A1" s="87" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+    </row>
+    <row r="2" spans="1:7" ht="28">
       <c r="A2" s="6" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="57" t="s">
-        <v>322</v>
+      <c r="D2" s="56" t="s">
+        <v>319</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>9</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="H2" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="56" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="56" t="s">
-        <v>7</v>
-      </c>
-      <c r="K2" s="58" t="s">
-        <v>322</v>
-      </c>
-      <c r="L2" s="56" t="s">
-        <v>332</v>
-      </c>
-      <c r="M2" s="56" t="s">
-        <v>9</v>
-      </c>
-      <c r="N2" s="59" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="42">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="42">
       <c r="A3" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="57" t="s">
         <v>23</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="60" t="s">
-        <v>25</v>
       </c>
       <c r="D3" s="19">
         <v>7200</v>
@@ -4500,38 +4312,16 @@
         <f t="shared" ref="G3:G23" si="0">E3*F3</f>
         <v>18000</v>
       </c>
-      <c r="H3" s="61" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="61" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="62" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" s="61">
-        <v>1200</v>
-      </c>
-      <c r="L3" s="61">
-        <v>0</v>
-      </c>
-      <c r="M3" s="61">
-        <v>18</v>
-      </c>
-      <c r="N3" s="61">
-        <f t="shared" ref="N3:N23" si="1">L3*M3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="42">
+    </row>
+    <row r="4" spans="1:7" ht="42">
       <c r="A4" s="19" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="63" t="s">
-        <v>29</v>
+        <v>16</v>
+      </c>
+      <c r="C4" s="58" t="s">
+        <v>27</v>
       </c>
       <c r="D4" s="19">
         <v>7200</v>
@@ -4546,38 +4336,16 @@
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="H4" s="61" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" s="61" t="s">
-        <v>24</v>
-      </c>
-      <c r="J4" s="64" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" s="61">
-        <v>1200</v>
-      </c>
-      <c r="L4" s="61">
-        <v>0</v>
-      </c>
-      <c r="M4" s="61">
-        <v>3</v>
-      </c>
-      <c r="N4" s="61">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="42">
+    </row>
+    <row r="5" spans="1:7" ht="42">
       <c r="A5" s="19" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="65" t="s">
-        <v>35</v>
+        <v>16</v>
+      </c>
+      <c r="C5" s="59" t="s">
+        <v>33</v>
       </c>
       <c r="D5" s="19">
         <v>7200</v>
@@ -4592,38 +4360,16 @@
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="H5" s="61" t="s">
-        <v>34</v>
-      </c>
-      <c r="I5" s="61" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="66" t="s">
+    </row>
+    <row r="6" spans="1:7" ht="42">
+      <c r="A6" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="K5" s="61">
-        <v>1200</v>
-      </c>
-      <c r="L5" s="61">
-        <v>0</v>
-      </c>
-      <c r="M5" s="61">
-        <v>3</v>
-      </c>
-      <c r="N5" s="61">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="42">
-      <c r="A6" s="19" t="s">
-        <v>37</v>
-      </c>
       <c r="B6" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="67" t="s">
-        <v>38</v>
+        <v>16</v>
+      </c>
+      <c r="C6" s="60" t="s">
+        <v>36</v>
       </c>
       <c r="D6" s="19">
         <v>7200</v>
@@ -4638,38 +4384,16 @@
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="H6" s="61" t="s">
-        <v>37</v>
-      </c>
-      <c r="I6" s="61" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="68" t="s">
-        <v>38</v>
-      </c>
-      <c r="K6" s="61">
-        <v>1200</v>
-      </c>
-      <c r="L6" s="61">
-        <v>0</v>
-      </c>
-      <c r="M6" s="61">
-        <v>3</v>
-      </c>
-      <c r="N6" s="61">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="42">
+    </row>
+    <row r="7" spans="1:7" ht="42">
       <c r="A7" s="19" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="69" t="s">
-        <v>43</v>
+        <v>16</v>
+      </c>
+      <c r="C7" s="61" t="s">
+        <v>41</v>
       </c>
       <c r="D7" s="19">
         <v>7200</v>
@@ -4684,38 +4408,16 @@
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="H7" s="61" t="s">
-        <v>42</v>
-      </c>
-      <c r="I7" s="61" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="70" t="s">
-        <v>43</v>
-      </c>
-      <c r="K7" s="61">
-        <v>1200</v>
-      </c>
-      <c r="L7" s="61">
-        <v>0</v>
-      </c>
-      <c r="M7" s="61">
-        <v>3</v>
-      </c>
-      <c r="N7" s="61">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="42">
+    </row>
+    <row r="8" spans="1:7" ht="42">
       <c r="A8" s="19" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="71" t="s">
-        <v>47</v>
+        <v>16</v>
+      </c>
+      <c r="C8" s="62" t="s">
+        <v>45</v>
       </c>
       <c r="D8" s="19">
         <v>7200</v>
@@ -4724,44 +4426,22 @@
         <v>1000</v>
       </c>
       <c r="F8" s="19">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G8" s="19">
         <f t="shared" si="0"/>
-        <v>9000</v>
-      </c>
-      <c r="H8" s="61" t="s">
-        <v>46</v>
-      </c>
-      <c r="I8" s="61" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8" s="72" t="s">
-        <v>47</v>
-      </c>
-      <c r="K8" s="61">
-        <v>1200</v>
-      </c>
-      <c r="L8" s="61">
-        <v>0</v>
-      </c>
-      <c r="M8" s="61">
-        <v>9</v>
-      </c>
-      <c r="N8" s="61">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="42">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="42">
       <c r="A9" s="19" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="73" t="s">
-        <v>51</v>
+        <v>16</v>
+      </c>
+      <c r="C9" s="63" t="s">
+        <v>49</v>
       </c>
       <c r="D9" s="19">
         <v>7200</v>
@@ -4776,38 +4456,16 @@
         <f t="shared" si="0"/>
         <v>9000</v>
       </c>
-      <c r="H9" s="61" t="s">
-        <v>50</v>
-      </c>
-      <c r="I9" s="61" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9" s="74" t="s">
-        <v>51</v>
-      </c>
-      <c r="K9" s="61">
-        <v>1200</v>
-      </c>
-      <c r="L9" s="61">
-        <v>0</v>
-      </c>
-      <c r="M9" s="61">
-        <v>9</v>
-      </c>
-      <c r="N9" s="61">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="42">
+    </row>
+    <row r="10" spans="1:7" ht="42">
       <c r="A10" s="19" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="75" t="s">
-        <v>58</v>
+        <v>16</v>
+      </c>
+      <c r="C10" s="64" t="s">
+        <v>56</v>
       </c>
       <c r="D10" s="19">
         <v>7200</v>
@@ -4816,44 +4474,22 @@
         <v>1000</v>
       </c>
       <c r="F10" s="19">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G10" s="19">
         <f t="shared" si="0"/>
-        <v>6000</v>
-      </c>
-      <c r="H10" s="61" t="s">
-        <v>57</v>
-      </c>
-      <c r="I10" s="61" t="s">
-        <v>24</v>
-      </c>
-      <c r="J10" s="76" t="s">
-        <v>58</v>
-      </c>
-      <c r="K10" s="61">
-        <v>1200</v>
-      </c>
-      <c r="L10" s="61">
-        <v>0</v>
-      </c>
-      <c r="M10" s="61">
-        <v>6</v>
-      </c>
-      <c r="N10" s="61">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="42">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="42">
       <c r="A11" s="19" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="77" t="s">
-        <v>62</v>
+        <v>16</v>
+      </c>
+      <c r="C11" s="65" t="s">
+        <v>60</v>
       </c>
       <c r="D11" s="19">
         <v>7200</v>
@@ -4868,38 +4504,16 @@
         <f t="shared" si="0"/>
         <v>5000</v>
       </c>
-      <c r="H11" s="61" t="s">
-        <v>61</v>
-      </c>
-      <c r="I11" s="61" t="s">
-        <v>24</v>
-      </c>
-      <c r="J11" s="78" t="s">
-        <v>62</v>
-      </c>
-      <c r="K11" s="61">
-        <v>1200</v>
-      </c>
-      <c r="L11" s="61">
-        <v>0</v>
-      </c>
-      <c r="M11" s="61">
-        <v>5</v>
-      </c>
-      <c r="N11" s="61">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="42">
+    </row>
+    <row r="12" spans="1:7" ht="42">
       <c r="A12" s="19" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="79" t="s">
-        <v>67</v>
+        <v>16</v>
+      </c>
+      <c r="C12" s="66" t="s">
+        <v>65</v>
       </c>
       <c r="D12" s="19">
         <v>7200</v>
@@ -4908,44 +4522,22 @@
         <v>1000</v>
       </c>
       <c r="F12" s="19">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G12" s="19">
         <f t="shared" si="0"/>
-        <v>8000</v>
-      </c>
-      <c r="H12" s="61" t="s">
-        <v>66</v>
-      </c>
-      <c r="I12" s="61" t="s">
-        <v>24</v>
-      </c>
-      <c r="J12" s="80" t="s">
-        <v>67</v>
-      </c>
-      <c r="K12" s="61">
-        <v>1200</v>
-      </c>
-      <c r="L12" s="61">
-        <v>0</v>
-      </c>
-      <c r="M12" s="61">
-        <v>8</v>
-      </c>
-      <c r="N12" s="61">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="42">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="42">
       <c r="A13" s="19" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="81" t="s">
-        <v>72</v>
+        <v>16</v>
+      </c>
+      <c r="C13" s="67" t="s">
+        <v>70</v>
       </c>
       <c r="D13" s="19">
         <v>7200</v>
@@ -4954,44 +4546,22 @@
         <v>1000</v>
       </c>
       <c r="F13" s="19">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G13" s="19">
         <f t="shared" si="0"/>
-        <v>8000</v>
-      </c>
-      <c r="H13" s="61" t="s">
-        <v>71</v>
-      </c>
-      <c r="I13" s="61" t="s">
-        <v>24</v>
-      </c>
-      <c r="J13" s="82" t="s">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="42">
+      <c r="A14" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="K13" s="61">
-        <v>1200</v>
-      </c>
-      <c r="L13" s="61">
-        <v>0</v>
-      </c>
-      <c r="M13" s="61">
-        <v>8</v>
-      </c>
-      <c r="N13" s="61">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="42">
-      <c r="A14" s="19" t="s">
-        <v>74</v>
-      </c>
       <c r="B14" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="83" t="s">
-        <v>75</v>
+        <v>16</v>
+      </c>
+      <c r="C14" s="68" t="s">
+        <v>73</v>
       </c>
       <c r="D14" s="19">
         <v>7200</v>
@@ -5000,44 +4570,22 @@
         <v>1000</v>
       </c>
       <c r="F14" s="19">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G14" s="19">
         <f t="shared" si="0"/>
-        <v>8000</v>
-      </c>
-      <c r="H14" s="61" t="s">
-        <v>74</v>
-      </c>
-      <c r="I14" s="61" t="s">
-        <v>24</v>
-      </c>
-      <c r="J14" s="84" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="42">
+      <c r="A15" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="K14" s="61">
-        <v>1200</v>
-      </c>
-      <c r="L14" s="61">
-        <v>0</v>
-      </c>
-      <c r="M14" s="61">
-        <v>8</v>
-      </c>
-      <c r="N14" s="61">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="42">
-      <c r="A15" s="19" t="s">
-        <v>77</v>
-      </c>
       <c r="B15" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="85" t="s">
-        <v>78</v>
+        <v>16</v>
+      </c>
+      <c r="C15" s="69" t="s">
+        <v>76</v>
       </c>
       <c r="D15" s="19">
         <v>7200</v>
@@ -5046,44 +4594,22 @@
         <v>1000</v>
       </c>
       <c r="F15" s="19">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G15" s="19">
         <f t="shared" si="0"/>
-        <v>3000</v>
-      </c>
-      <c r="H15" s="61" t="s">
-        <v>77</v>
-      </c>
-      <c r="I15" s="61" t="s">
-        <v>24</v>
-      </c>
-      <c r="J15" s="86" t="s">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="42">
+      <c r="A16" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="K15" s="61">
-        <v>1200</v>
-      </c>
-      <c r="L15" s="61">
-        <v>0</v>
-      </c>
-      <c r="M15" s="61">
-        <v>3</v>
-      </c>
-      <c r="N15" s="61">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="42">
-      <c r="A16" s="19" t="s">
-        <v>80</v>
-      </c>
       <c r="B16" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="87" t="s">
-        <v>81</v>
+        <v>16</v>
+      </c>
+      <c r="C16" s="70" t="s">
+        <v>79</v>
       </c>
       <c r="D16" s="19">
         <v>7200</v>
@@ -5092,44 +4618,22 @@
         <v>1000</v>
       </c>
       <c r="F16" s="19">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G16" s="19">
         <f t="shared" si="0"/>
-        <v>10000</v>
-      </c>
-      <c r="H16" s="61" t="s">
-        <v>80</v>
-      </c>
-      <c r="I16" s="61" t="s">
-        <v>24</v>
-      </c>
-      <c r="J16" s="88" t="s">
-        <v>81</v>
-      </c>
-      <c r="K16" s="61">
-        <v>1200</v>
-      </c>
-      <c r="L16" s="61">
-        <v>0</v>
-      </c>
-      <c r="M16" s="61">
-        <v>10</v>
-      </c>
-      <c r="N16" s="61">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="42">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="42">
       <c r="A17" s="19" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="89" t="s">
-        <v>85</v>
+        <v>16</v>
+      </c>
+      <c r="C17" s="71" t="s">
+        <v>83</v>
       </c>
       <c r="D17" s="19">
         <v>7200</v>
@@ -5144,38 +4648,16 @@
         <f t="shared" si="0"/>
         <v>4000</v>
       </c>
-      <c r="H17" s="61" t="s">
-        <v>84</v>
-      </c>
-      <c r="I17" s="61" t="s">
-        <v>24</v>
-      </c>
-      <c r="J17" s="90" t="s">
-        <v>85</v>
-      </c>
-      <c r="K17" s="61">
-        <v>1200</v>
-      </c>
-      <c r="L17" s="61">
-        <v>0</v>
-      </c>
-      <c r="M17" s="61">
-        <v>4</v>
-      </c>
-      <c r="N17" s="61">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="42">
+    </row>
+    <row r="18" spans="1:7" ht="42">
       <c r="A18" s="19" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" s="91" t="s">
-        <v>90</v>
+        <v>16</v>
+      </c>
+      <c r="C18" s="72" t="s">
+        <v>88</v>
       </c>
       <c r="D18" s="19">
         <v>7200</v>
@@ -5190,38 +4672,16 @@
         <f t="shared" si="0"/>
         <v>4000</v>
       </c>
-      <c r="H18" s="61" t="s">
+    </row>
+    <row r="19" spans="1:7" ht="42">
+      <c r="A19" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="I18" s="61" t="s">
-        <v>24</v>
-      </c>
-      <c r="J18" s="92" t="s">
+      <c r="B19" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="73" t="s">
         <v>90</v>
-      </c>
-      <c r="K18" s="61">
-        <v>1200</v>
-      </c>
-      <c r="L18" s="61">
-        <v>0</v>
-      </c>
-      <c r="M18" s="61">
-        <v>4</v>
-      </c>
-      <c r="N18" s="61">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="42">
-      <c r="A19" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="B19" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" s="93" t="s">
-        <v>92</v>
       </c>
       <c r="D19" s="19">
         <v>7200</v>
@@ -5236,38 +4696,16 @@
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="H19" s="61" t="s">
+    </row>
+    <row r="20" spans="1:7" ht="42">
+      <c r="A20" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="I19" s="61" t="s">
-        <v>24</v>
-      </c>
-      <c r="J19" s="94" t="s">
+      <c r="B20" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="74" t="s">
         <v>92</v>
-      </c>
-      <c r="K19" s="61">
-        <v>1200</v>
-      </c>
-      <c r="L19" s="61">
-        <v>0</v>
-      </c>
-      <c r="M19" s="61">
-        <v>3</v>
-      </c>
-      <c r="N19" s="61">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="42">
-      <c r="A20" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" s="95" t="s">
-        <v>94</v>
       </c>
       <c r="D20" s="19">
         <v>7200</v>
@@ -5282,38 +4720,16 @@
         <f t="shared" si="0"/>
         <v>4000</v>
       </c>
-      <c r="H20" s="61" t="s">
+    </row>
+    <row r="21" spans="1:7" ht="42">
+      <c r="A21" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="I20" s="61" t="s">
-        <v>24</v>
-      </c>
-      <c r="J20" s="96" t="s">
+      <c r="B21" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="75" t="s">
         <v>94</v>
-      </c>
-      <c r="K20" s="61">
-        <v>1200</v>
-      </c>
-      <c r="L20" s="61">
-        <v>0</v>
-      </c>
-      <c r="M20" s="61">
-        <v>4</v>
-      </c>
-      <c r="N20" s="61">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="42">
-      <c r="A21" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" s="97" t="s">
-        <v>96</v>
       </c>
       <c r="D21" s="19">
         <v>7200</v>
@@ -5328,38 +4744,16 @@
         <f t="shared" si="0"/>
         <v>4000</v>
       </c>
-      <c r="H21" s="61" t="s">
+    </row>
+    <row r="22" spans="1:7" ht="42">
+      <c r="A22" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="I21" s="61" t="s">
-        <v>24</v>
-      </c>
-      <c r="J21" s="98" t="s">
+      <c r="B22" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="76" t="s">
         <v>96</v>
-      </c>
-      <c r="K21" s="61">
-        <v>1200</v>
-      </c>
-      <c r="L21" s="61">
-        <v>0</v>
-      </c>
-      <c r="M21" s="61">
-        <v>4</v>
-      </c>
-      <c r="N21" s="61">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="42">
-      <c r="A22" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" s="99" t="s">
-        <v>98</v>
       </c>
       <c r="D22" s="19">
         <v>7200</v>
@@ -5374,38 +4768,16 @@
         <f t="shared" si="0"/>
         <v>5000</v>
       </c>
-      <c r="H22" s="61" t="s">
+    </row>
+    <row r="23" spans="1:7" ht="42">
+      <c r="A23" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="I22" s="61" t="s">
-        <v>24</v>
-      </c>
-      <c r="J22" s="100" t="s">
+      <c r="B23" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="77" t="s">
         <v>98</v>
-      </c>
-      <c r="K22" s="61">
-        <v>1200</v>
-      </c>
-      <c r="L22" s="61">
-        <v>0</v>
-      </c>
-      <c r="M22" s="61">
-        <v>5</v>
-      </c>
-      <c r="N22" s="61">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="42">
-      <c r="A23" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C23" s="101" t="s">
-        <v>100</v>
       </c>
       <c r="D23" s="19">
         <v>7200</v>
@@ -5420,57 +4792,27 @@
         <f t="shared" si="0"/>
         <v>7000</v>
       </c>
-      <c r="H23" s="61" t="s">
-        <v>99</v>
-      </c>
-      <c r="I23" s="61" t="s">
-        <v>24</v>
-      </c>
-      <c r="J23" s="102" t="s">
-        <v>100</v>
-      </c>
-      <c r="K23" s="61">
-        <v>1200</v>
-      </c>
-      <c r="L23" s="61">
-        <v>0</v>
-      </c>
-      <c r="M23" s="61">
-        <v>7</v>
-      </c>
-      <c r="N23" s="61">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
-      <c r="A24" s="103" t="s">
-        <v>333</v>
-      </c>
-      <c r="B24" s="103"/>
-      <c r="C24" s="103"/>
-      <c r="D24" s="103"/>
-      <c r="E24" s="103"/>
-      <c r="F24" s="103">
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="78" t="s">
+        <v>328</v>
+      </c>
+      <c r="B24" s="78"/>
+      <c r="C24" s="78"/>
+      <c r="D24" s="78"/>
+      <c r="E24" s="78"/>
+      <c r="F24" s="78">
         <f>SUM(F3:F23)</f>
-        <v>127</v>
-      </c>
-      <c r="G24" s="103">
+        <v>111</v>
+      </c>
+      <c r="G24" s="78">
         <f>SUM(G3:G23)</f>
-        <v>127000</v>
-      </c>
-      <c r="H24" s="103"/>
-      <c r="I24" s="103"/>
-      <c r="J24" s="103"/>
-      <c r="K24" s="103"/>
-      <c r="L24" s="103"/>
-      <c r="M24" s="103"/>
-      <c r="N24" s="103"/>
+        <v>111000</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="H1:N1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5482,141 +4824,141 @@
   <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="20.1640625" customWidth="1"/>
+    <col min="1" max="1" width="27.83203125" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
     <col min="4" max="4" width="25.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="34">
-      <c r="A1" s="103" t="s">
-        <v>331</v>
-      </c>
-      <c r="B1" s="103" t="s">
-        <v>328</v>
-      </c>
-      <c r="C1" s="104" t="s">
+      <c r="A1" s="78" t="s">
+        <v>326</v>
+      </c>
+      <c r="B1" s="78" t="s">
+        <v>323</v>
+      </c>
+      <c r="C1" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="105" t="s">
-        <v>318</v>
+      <c r="D1" s="80" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="103" t="s">
-        <v>327</v>
-      </c>
-      <c r="B2" s="103">
-        <v>1</v>
-      </c>
-      <c r="C2" s="103">
+      <c r="A2" s="78" t="s">
+        <v>322</v>
+      </c>
+      <c r="B2" s="78">
+        <v>3</v>
+      </c>
+      <c r="C2" s="78">
         <v>200</v>
       </c>
-      <c r="D2" s="103">
+      <c r="D2" s="78">
         <f>C2*B2</f>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="78" t="s">
+        <v>343</v>
+      </c>
+      <c r="B3" s="78">
+        <v>10</v>
+      </c>
+      <c r="C3" s="78">
         <v>200</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="103" t="s">
-        <v>326</v>
-      </c>
-      <c r="B3" s="103">
-        <v>7</v>
-      </c>
-      <c r="C3" s="103">
+      <c r="D3" s="78">
+        <f t="shared" ref="D3:D8" si="0">C3*B3</f>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="78" t="s">
+        <v>344</v>
+      </c>
+      <c r="B4" s="78">
+        <v>4</v>
+      </c>
+      <c r="C4" s="78">
         <v>200</v>
       </c>
-      <c r="D3" s="103">
-        <f t="shared" ref="D3:D8" si="0">C3*B3</f>
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="B4" s="103">
-        <v>5</v>
-      </c>
-      <c r="C4" s="103">
+      <c r="D4" s="78">
+        <f t="shared" si="0"/>
+        <v>800</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="78" t="s">
+        <v>325</v>
+      </c>
+      <c r="B5" s="78">
+        <v>3</v>
+      </c>
+      <c r="C5" s="78">
         <v>200</v>
       </c>
-      <c r="D4" s="103">
-        <f t="shared" si="0"/>
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="103" t="s">
-        <v>330</v>
-      </c>
-      <c r="B5" s="103">
-        <v>3</v>
-      </c>
-      <c r="C5" s="103">
-        <v>200</v>
-      </c>
-      <c r="D5" s="103">
+      <c r="D5" s="78">
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="103" t="s">
-        <v>329</v>
-      </c>
-      <c r="B6" s="103">
+      <c r="A6" s="78" t="s">
+        <v>324</v>
+      </c>
+      <c r="B6" s="78">
         <v>4</v>
       </c>
-      <c r="C6" s="103">
+      <c r="C6" s="78">
         <v>200</v>
       </c>
-      <c r="D6" s="103">
+      <c r="D6" s="78">
         <f t="shared" si="0"/>
         <v>800</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="103" t="s">
-        <v>325</v>
-      </c>
-      <c r="B7" s="103">
+      <c r="A7" s="78" t="s">
+        <v>321</v>
+      </c>
+      <c r="B7" s="78">
         <v>10</v>
       </c>
-      <c r="C7" s="103">
+      <c r="C7" s="78">
         <v>200</v>
       </c>
-      <c r="D7" s="103">
+      <c r="D7" s="78">
         <f t="shared" si="0"/>
         <v>2000</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="106" t="s">
-        <v>334</v>
-      </c>
-      <c r="B8" s="116">
-        <v>146</v>
-      </c>
-      <c r="C8" s="116">
+    <row r="8" spans="1:4" ht="17" thickBot="1">
+      <c r="A8" s="94" t="s">
+        <v>342</v>
+      </c>
+      <c r="B8" s="94">
+        <v>13</v>
+      </c>
+      <c r="C8" s="94">
         <v>200</v>
       </c>
-      <c r="D8" s="116">
+      <c r="D8" s="94">
         <f t="shared" si="0"/>
-        <v>29200</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="106" t="s">
-        <v>333</v>
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="17" thickTop="1">
+      <c r="A9" s="81" t="s">
+        <v>328</v>
       </c>
       <c r="B9">
         <f>SUM(B2:B8)</f>
-        <v>176</v>
+        <v>47</v>
       </c>
       <c r="D9">
         <f>SUM(D2:D8)</f>
-        <v>35200</v>
+        <v>9400</v>
       </c>
     </row>
   </sheetData>
@@ -5626,6 +4968,198 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{356B98DB-4BDE-8445-BB31-2082C11C84A0}">
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="78" t="s">
+        <v>340</v>
+      </c>
+      <c r="B1" s="78" t="s">
+        <v>329</v>
+      </c>
+      <c r="C1" s="78" t="s">
+        <v>330</v>
+      </c>
+      <c r="D1" s="90" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="78" t="s">
+        <v>331</v>
+      </c>
+      <c r="B2" s="78">
+        <v>108</v>
+      </c>
+      <c r="C2" s="78">
+        <v>5</v>
+      </c>
+      <c r="D2" s="78">
+        <f>B2+C2</f>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="78" t="s">
+        <v>332</v>
+      </c>
+      <c r="B3" s="78">
+        <v>10</v>
+      </c>
+      <c r="C3" s="78">
+        <v>0</v>
+      </c>
+      <c r="D3" s="78">
+        <f t="shared" ref="D3:D10" si="0">B3+C3</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="78" t="s">
+        <v>333</v>
+      </c>
+      <c r="B4" s="78">
+        <v>48</v>
+      </c>
+      <c r="C4" s="78">
+        <v>44</v>
+      </c>
+      <c r="D4" s="78">
+        <f t="shared" si="0"/>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="78" t="s">
+        <v>334</v>
+      </c>
+      <c r="B5" s="78">
+        <v>49</v>
+      </c>
+      <c r="C5" s="78">
+        <f>19+15</f>
+        <v>34</v>
+      </c>
+      <c r="D5" s="78">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="78" t="s">
+        <v>335</v>
+      </c>
+      <c r="B6" s="78">
+        <v>104</v>
+      </c>
+      <c r="C6" s="78">
+        <v>23</v>
+      </c>
+      <c r="D6" s="78">
+        <f t="shared" si="0"/>
+        <v>127</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="78" t="s">
+        <v>336</v>
+      </c>
+      <c r="B7" s="78">
+        <v>69</v>
+      </c>
+      <c r="C7" s="78">
+        <v>20</v>
+      </c>
+      <c r="D7" s="78">
+        <f t="shared" si="0"/>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="78" t="s">
+        <v>337</v>
+      </c>
+      <c r="B8" s="78">
+        <v>3</v>
+      </c>
+      <c r="C8" s="78">
+        <v>1</v>
+      </c>
+      <c r="D8" s="78">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="78" t="s">
+        <v>338</v>
+      </c>
+      <c r="B9" s="78">
+        <v>1</v>
+      </c>
+      <c r="C9" s="78">
+        <v>2</v>
+      </c>
+      <c r="D9" s="78">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="17" thickBot="1">
+      <c r="A10" s="91" t="s">
+        <v>339</v>
+      </c>
+      <c r="B10" s="91">
+        <v>0</v>
+      </c>
+      <c r="C10" s="91">
+        <v>13</v>
+      </c>
+      <c r="D10" s="91">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="17" thickTop="1">
+      <c r="A11" s="92" t="s">
+        <v>328</v>
+      </c>
+      <c r="B11" s="93">
+        <f>SUM(B2:B10)</f>
+        <v>392</v>
+      </c>
+      <c r="C11" s="93">
+        <f>SUM(C2:C10)</f>
+        <v>142</v>
+      </c>
+      <c r="D11" s="92">
+        <f>B11+C11</f>
+        <v>534</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>341</v>
+      </c>
+      <c r="D12">
+        <f>应用产品!L20+应用产品!S20+应用产品!Z20+应用产品!AG20+基础软件!F24+其他业务!B9</f>
+        <v>534</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A30F8D0D-3D65-D349-8378-463C11B69773}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -5642,1253 +5176,1253 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A2" s="88" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A2" s="114" t="s">
+    <row r="3" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A3" s="89"/>
+      <c r="B3" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B2" s="1" t="s">
+    </row>
+    <row r="4" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A4" s="89"/>
+      <c r="B4" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A3" s="115"/>
-      <c r="B3" s="1" t="s">
+    <row r="5" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A5" s="89"/>
+      <c r="B5" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A4" s="115"/>
-      <c r="B4" s="1" t="s">
+    <row r="6" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A6" s="89"/>
+      <c r="B6" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A5" s="115"/>
-      <c r="B5" s="1" t="s">
+    <row r="7" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A7" s="89"/>
+      <c r="B7" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A6" s="115"/>
-      <c r="B6" s="1" t="s">
+    <row r="8" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A8" s="89"/>
+      <c r="B8" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A7" s="115"/>
-      <c r="B7" s="1" t="s">
+    <row r="9" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A9" s="89"/>
+      <c r="B9" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A8" s="115"/>
-      <c r="B8" s="1" t="s">
+    <row r="10" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A10" s="89"/>
+      <c r="B10" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A9" s="115"/>
-      <c r="B9" s="1" t="s">
+    <row r="11" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A11" s="89"/>
+      <c r="B11" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A10" s="115"/>
-      <c r="B10" s="1" t="s">
+    <row r="12" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A12" s="89"/>
+      <c r="B12" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A11" s="115"/>
-      <c r="B11" s="1" t="s">
+    <row r="13" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A13" s="89"/>
+      <c r="B13" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A12" s="115"/>
-      <c r="B12" s="1" t="s">
+    <row r="14" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A14" s="89"/>
+      <c r="B14" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A13" s="115"/>
-      <c r="B13" s="1" t="s">
+    <row r="15" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A15" s="89"/>
+      <c r="B15" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A14" s="115"/>
-      <c r="B14" s="1" t="s">
+    <row r="16" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A16" s="89"/>
+      <c r="B16" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A15" s="115"/>
-      <c r="B15" s="1" t="s">
+    <row r="17" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A17" s="89"/>
+      <c r="B17" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A16" s="115"/>
-      <c r="B16" s="1" t="s">
+    <row r="18" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A18" s="89"/>
+      <c r="B18" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A17" s="115"/>
-      <c r="B17" s="1" t="s">
+    <row r="19" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A19" s="89"/>
+      <c r="B19" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A18" s="115"/>
-      <c r="B18" s="1" t="s">
+    <row r="20" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A20" s="89"/>
+      <c r="B20" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A19" s="115"/>
-      <c r="B19" s="1" t="s">
+    <row r="21" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A21" s="89"/>
+      <c r="B21" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A20" s="115"/>
-      <c r="B20" s="1" t="s">
+    <row r="22" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A22" s="89"/>
+      <c r="B22" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A21" s="115"/>
-      <c r="B21" s="1" t="s">
+    <row r="23" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A23" s="89"/>
+      <c r="B23" s="1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A22" s="115"/>
-      <c r="B22" s="1" t="s">
+    <row r="24" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A24" s="89"/>
+      <c r="B24" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A23" s="115"/>
-      <c r="B23" s="1" t="s">
+    <row r="25" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A25" s="88" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A24" s="115"/>
-      <c r="B24" s="1" t="s">
+      <c r="B25" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A25" s="114" t="s">
+    <row r="26" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A26" s="89"/>
+      <c r="B26" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B25" s="1" t="s">
+    </row>
+    <row r="27" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A27" s="89"/>
+      <c r="B27" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A26" s="115"/>
-      <c r="B26" s="1" t="s">
+    <row r="28" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A28" s="89"/>
+      <c r="B28" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A27" s="115"/>
-      <c r="B27" s="1" t="s">
+    <row r="29" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A29" s="89"/>
+      <c r="B29" s="1" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A28" s="115"/>
-      <c r="B28" s="1" t="s">
+    <row r="30" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A30" s="89"/>
+      <c r="B30" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A29" s="115"/>
-      <c r="B29" s="1" t="s">
+    <row r="31" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A31" s="89"/>
+      <c r="B31" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A30" s="115"/>
-      <c r="B30" s="1" t="s">
+    <row r="32" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A32" s="89"/>
+      <c r="B32" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A31" s="115"/>
-      <c r="B31" s="1" t="s">
+    <row r="33" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A33" s="88" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A32" s="115"/>
-      <c r="B32" s="1" t="s">
+      <c r="B33" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A33" s="114" t="s">
+    <row r="34" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A34" s="89"/>
+      <c r="B34" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B33" s="1" t="s">
+    </row>
+    <row r="35" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A35" s="89"/>
+      <c r="B35" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A34" s="115"/>
-      <c r="B34" s="1" t="s">
+    <row r="36" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A36" s="89"/>
+      <c r="B36" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A35" s="115"/>
-      <c r="B35" s="1" t="s">
+    <row r="37" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A37" s="89"/>
+      <c r="B37" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A36" s="115"/>
-      <c r="B36" s="1" t="s">
+    <row r="38" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A38" s="89"/>
+      <c r="B38" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A37" s="115"/>
-      <c r="B37" s="1" t="s">
+    <row r="39" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A39" s="89"/>
+      <c r="B39" s="1" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A38" s="115"/>
-      <c r="B38" s="1" t="s">
+    <row r="40" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A40" s="89"/>
+      <c r="B40" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A39" s="115"/>
-      <c r="B39" s="1" t="s">
+    <row r="41" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A41" s="89"/>
+      <c r="B41" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A40" s="115"/>
-      <c r="B40" s="1" t="s">
+    <row r="42" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A42" s="89"/>
+      <c r="B42" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A41" s="115"/>
-      <c r="B41" s="1" t="s">
+    <row r="43" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A43" s="89"/>
+      <c r="B43" s="1" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A42" s="115"/>
-      <c r="B42" s="1" t="s">
+    <row r="44" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A44" s="89"/>
+      <c r="B44" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A43" s="115"/>
-      <c r="B43" s="1" t="s">
+    <row r="45" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A45" s="89"/>
+      <c r="B45" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A44" s="115"/>
-      <c r="B44" s="1" t="s">
+    <row r="46" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A46" s="89"/>
+      <c r="B46" s="1" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A45" s="115"/>
-      <c r="B45" s="1" t="s">
+    <row r="47" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A47" s="89"/>
+      <c r="B47" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A46" s="115"/>
-      <c r="B46" s="1" t="s">
+    <row r="48" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A48" s="88" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A47" s="115"/>
-      <c r="B47" s="1" t="s">
+      <c r="B48" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A48" s="114" t="s">
+    <row r="49" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A49" s="89"/>
+      <c r="B49" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B48" s="1" t="s">
+    </row>
+    <row r="50" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A50" s="89"/>
+      <c r="B50" s="1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A49" s="115"/>
-      <c r="B49" s="1" t="s">
+    <row r="51" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A51" s="89"/>
+      <c r="B51" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A50" s="115"/>
-      <c r="B50" s="1" t="s">
+    <row r="52" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A52" s="89"/>
+      <c r="B52" s="1" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A51" s="115"/>
-      <c r="B51" s="1" t="s">
+    <row r="53" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A53" s="89"/>
+      <c r="B53" s="1" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A52" s="115"/>
-      <c r="B52" s="1" t="s">
+    <row r="54" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A54" s="89"/>
+      <c r="B54" s="1" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A53" s="115"/>
-      <c r="B53" s="1" t="s">
+    <row r="55" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A55" s="88" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A54" s="115"/>
-      <c r="B54" s="1" t="s">
+      <c r="B55" s="1" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A55" s="114" t="s">
+    <row r="56" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A56" s="89"/>
+      <c r="B56" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B55" s="1" t="s">
+    </row>
+    <row r="57" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A57" s="89"/>
+      <c r="B57" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A56" s="115"/>
-      <c r="B56" s="1" t="s">
+    <row r="58" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A58" s="89"/>
+      <c r="B58" s="1" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A57" s="115"/>
-      <c r="B57" s="1" t="s">
+    <row r="59" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A59" s="89"/>
+      <c r="B59" s="1" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A58" s="115"/>
-      <c r="B58" s="1" t="s">
+    <row r="60" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A60" s="89"/>
+      <c r="B60" s="1" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A59" s="115"/>
-      <c r="B59" s="1" t="s">
+    <row r="61" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A61" s="89"/>
+      <c r="B61" s="1" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A60" s="115"/>
-      <c r="B60" s="1" t="s">
+    <row r="62" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A62" s="89"/>
+      <c r="B62" s="1" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A61" s="115"/>
-      <c r="B61" s="1" t="s">
+    <row r="63" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A63" s="89"/>
+      <c r="B63" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A62" s="115"/>
-      <c r="B62" s="1" t="s">
+    <row r="64" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A64" s="89"/>
+      <c r="B64" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A63" s="115"/>
-      <c r="B63" s="1" t="s">
+    <row r="65" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A65" s="89"/>
+      <c r="B65" s="1" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A64" s="115"/>
-      <c r="B64" s="1" t="s">
+    <row r="66" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A66" s="89"/>
+      <c r="B66" s="1" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A65" s="115"/>
-      <c r="B65" s="1" t="s">
+    <row r="67" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A67" s="88" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A66" s="115"/>
-      <c r="B66" s="1" t="s">
+      <c r="B67" s="1" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A67" s="114" t="s">
+    <row r="68" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A68" s="89"/>
+      <c r="B68" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B67" s="1" t="s">
+    </row>
+    <row r="69" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A69" s="89"/>
+      <c r="B69" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A68" s="115"/>
-      <c r="B68" s="1" t="s">
+    <row r="70" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A70" s="89"/>
+      <c r="B70" s="1" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A69" s="115"/>
-      <c r="B69" s="1" t="s">
+    <row r="71" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A71" s="89"/>
+      <c r="B71" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A72" s="89"/>
+      <c r="B72" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A70" s="115"/>
-      <c r="B70" s="1" t="s">
+    <row r="73" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A73" s="89"/>
+      <c r="B73" s="1" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A71" s="115"/>
-      <c r="B71" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A72" s="115"/>
-      <c r="B72" s="1" t="s">
+    <row r="74" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A74" s="89"/>
+      <c r="B74" s="1" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A73" s="115"/>
-      <c r="B73" s="1" t="s">
+    <row r="75" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A75" s="89"/>
+      <c r="B75" s="1" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A74" s="115"/>
-      <c r="B74" s="1" t="s">
+    <row r="76" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A76" s="89"/>
+      <c r="B76" s="1" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="75" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A75" s="115"/>
-      <c r="B75" s="1" t="s">
+    <row r="77" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A77" s="88" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="76" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A76" s="115"/>
-      <c r="B76" s="1" t="s">
+      <c r="B77" s="1" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="77" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A77" s="114" t="s">
+    <row r="78" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A78" s="89"/>
+      <c r="B78" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B77" s="1" t="s">
+    </row>
+    <row r="79" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A79" s="89"/>
+      <c r="B79" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A78" s="115"/>
-      <c r="B78" s="1" t="s">
+    <row r="80" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A80" s="89"/>
+      <c r="B80" s="1" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="79" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A79" s="115"/>
-      <c r="B79" s="1" t="s">
+    <row r="81" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A81" s="89"/>
+      <c r="B81" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="80" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A80" s="115"/>
-      <c r="B80" s="1" t="s">
+    <row r="82" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A82" s="89"/>
+      <c r="B82" s="1" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="81" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A81" s="115"/>
-      <c r="B81" s="1" t="s">
+    <row r="83" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A83" s="89"/>
+      <c r="B83" s="1" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="82" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A82" s="115"/>
-      <c r="B82" s="1" t="s">
+    <row r="84" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A84" s="89"/>
+      <c r="B84" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A85" s="89"/>
+      <c r="B85" s="1" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="83" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A83" s="115"/>
-      <c r="B83" s="1" t="s">
+    <row r="86" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A86" s="89"/>
+      <c r="B86" s="1" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="84" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A84" s="115"/>
-      <c r="B84" s="1" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A85" s="115"/>
-      <c r="B85" s="1" t="s">
+    <row r="87" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A87" s="89"/>
+      <c r="B87" s="1" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="86" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A86" s="115"/>
-      <c r="B86" s="1" t="s">
+    <row r="88" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A88" s="89"/>
+      <c r="B88" s="1" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="87" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A87" s="115"/>
-      <c r="B87" s="1" t="s">
+    <row r="89" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A89" s="89"/>
+      <c r="B89" s="1" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="88" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A88" s="115"/>
-      <c r="B88" s="1" t="s">
+    <row r="90" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A90" s="89"/>
+      <c r="B90" s="1" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="89" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A89" s="115"/>
-      <c r="B89" s="1" t="s">
+    <row r="91" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A91" s="89"/>
+      <c r="B91" s="1" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="90" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A90" s="115"/>
-      <c r="B90" s="1" t="s">
+    <row r="92" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A92" s="89"/>
+      <c r="B92" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="91" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A91" s="115"/>
-      <c r="B91" s="1" t="s">
+    <row r="93" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A93" s="89"/>
+      <c r="B93" s="1" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="92" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A92" s="115"/>
-      <c r="B92" s="1" t="s">
+    <row r="94" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A94" s="89"/>
+      <c r="B94" s="1" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="93" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A93" s="115"/>
-      <c r="B93" s="1" t="s">
+    <row r="95" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A95" s="89"/>
+      <c r="B95" s="1" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="94" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A94" s="115"/>
-      <c r="B94" s="1" t="s">
+    <row r="96" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A96" s="89"/>
+      <c r="B96" s="1" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="95" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A95" s="115"/>
-      <c r="B95" s="1" t="s">
+    <row r="97" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A97" s="89"/>
+      <c r="B97" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="96" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A96" s="115"/>
-      <c r="B96" s="1" t="s">
+    <row r="98" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A98" s="89"/>
+      <c r="B98" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="97" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A97" s="115"/>
-      <c r="B97" s="1" t="s">
+    <row r="99" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A99" s="89"/>
+      <c r="B99" s="1" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="98" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A98" s="115"/>
-      <c r="B98" s="1" t="s">
+    <row r="100" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A100" s="89"/>
+      <c r="B100" s="1" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="99" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A99" s="115"/>
-      <c r="B99" s="1" t="s">
+    <row r="101" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A101" s="89"/>
+      <c r="B101" s="1" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="100" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A100" s="115"/>
-      <c r="B100" s="1" t="s">
+    <row r="102" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A102" s="89"/>
+      <c r="B102" s="1" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="101" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A101" s="115"/>
-      <c r="B101" s="1" t="s">
+    <row r="103" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A103" s="89"/>
+      <c r="B103" s="1" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="102" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A102" s="115"/>
-      <c r="B102" s="1" t="s">
+    <row r="104" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A104" s="89"/>
+      <c r="B104" s="1" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="103" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A103" s="115"/>
-      <c r="B103" s="1" t="s">
+    <row r="105" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A105" s="89"/>
+      <c r="B105" s="1" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="104" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A104" s="115"/>
-      <c r="B104" s="1" t="s">
+    <row r="106" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A106" s="89"/>
+      <c r="B106" s="1" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="105" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A105" s="115"/>
-      <c r="B105" s="1" t="s">
+    <row r="107" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A107" s="89"/>
+      <c r="B107" s="1" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="106" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A106" s="115"/>
-      <c r="B106" s="1" t="s">
+    <row r="108" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A108" s="89"/>
+      <c r="B108" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="107" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A107" s="115"/>
-      <c r="B107" s="1" t="s">
+    <row r="109" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A109" s="89"/>
+      <c r="B109" s="1" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="108" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A108" s="115"/>
-      <c r="B108" s="1" t="s">
+    <row r="110" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A110" s="89"/>
+      <c r="B110" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="109" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A109" s="115"/>
-      <c r="B109" s="1" t="s">
+    <row r="111" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A111" s="89"/>
+      <c r="B111" s="1" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="110" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A110" s="115"/>
-      <c r="B110" s="1" t="s">
+    <row r="112" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A112" s="89"/>
+      <c r="B112" s="1" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="111" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A111" s="115"/>
-      <c r="B111" s="1" t="s">
+    <row r="113" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A113" s="89"/>
+      <c r="B113" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="112" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A112" s="115"/>
-      <c r="B112" s="1" t="s">
+    <row r="114" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A114" s="89"/>
+      <c r="B114" s="1" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="113" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A113" s="115"/>
-      <c r="B113" s="1" t="s">
+    <row r="115" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A115" s="89"/>
+      <c r="B115" s="1" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="114" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A114" s="115"/>
-      <c r="B114" s="1" t="s">
+    <row r="116" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A116" s="89"/>
+      <c r="B116" s="1" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="115" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A115" s="115"/>
-      <c r="B115" s="1" t="s">
+    <row r="117" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A117" s="89"/>
+      <c r="B117" s="1" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="116" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A116" s="115"/>
-      <c r="B116" s="1" t="s">
+    <row r="118" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A118" s="89"/>
+      <c r="B118" s="1" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="117" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A117" s="115"/>
-      <c r="B117" s="1" t="s">
+    <row r="119" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A119" s="89"/>
+      <c r="B119" s="1" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="118" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A118" s="115"/>
-      <c r="B118" s="1" t="s">
+    <row r="120" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A120" s="89"/>
+      <c r="B120" s="1" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="119" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A119" s="115"/>
-      <c r="B119" s="1" t="s">
+    <row r="121" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A121" s="89"/>
+      <c r="B121" s="1" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="120" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A120" s="115"/>
-      <c r="B120" s="1" t="s">
+    <row r="122" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A122" s="89"/>
+      <c r="B122" s="1" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="121" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A121" s="115"/>
-      <c r="B121" s="1" t="s">
+    <row r="123" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A123" s="89"/>
+      <c r="B123" s="1" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="122" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A122" s="115"/>
-      <c r="B122" s="1" t="s">
+    <row r="124" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A124" s="89"/>
+      <c r="B124" s="1" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="123" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A123" s="115"/>
-      <c r="B123" s="1" t="s">
+    <row r="125" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A125" s="88" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="124" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A124" s="115"/>
-      <c r="B124" s="1" t="s">
+      <c r="B125" s="1" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="125" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A125" s="114" t="s">
+    <row r="126" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A126" s="89"/>
+      <c r="B126" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B125" s="1" t="s">
+    </row>
+    <row r="127" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A127" s="89"/>
+      <c r="B127" s="1" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="126" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A126" s="115"/>
-      <c r="B126" s="1" t="s">
+    <row r="128" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A128" s="89"/>
+      <c r="B128" s="1" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="127" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A127" s="115"/>
-      <c r="B127" s="1" t="s">
+    <row r="129" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A129" s="89"/>
+      <c r="B129" s="1" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="128" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A128" s="115"/>
-      <c r="B128" s="1" t="s">
+    <row r="130" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A130" s="89"/>
+      <c r="B130" s="1" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="129" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A129" s="115"/>
-      <c r="B129" s="1" t="s">
+    <row r="131" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A131" s="89"/>
+      <c r="B131" s="1" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="130" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A130" s="115"/>
-      <c r="B130" s="1" t="s">
+    <row r="132" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A132" s="89"/>
+      <c r="B132" s="1" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="131" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A131" s="115"/>
-      <c r="B131" s="1" t="s">
+    <row r="133" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A133" s="89"/>
+      <c r="B133" s="1" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="132" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A132" s="115"/>
-      <c r="B132" s="1" t="s">
+    <row r="134" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A134" s="88" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="133" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A133" s="115"/>
-      <c r="B133" s="1" t="s">
+      <c r="B134" s="1" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="134" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A134" s="114" t="s">
+    <row r="135" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A135" s="89"/>
+      <c r="B135" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B134" s="1" t="s">
+    </row>
+    <row r="136" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A136" s="89"/>
+      <c r="B136" s="1" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="135" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A135" s="115"/>
-      <c r="B135" s="1" t="s">
+    <row r="137" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A137" s="89"/>
+      <c r="B137" s="1" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="136" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A136" s="115"/>
-      <c r="B136" s="1" t="s">
+    <row r="138" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A138" s="89"/>
+      <c r="B138" s="1" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="137" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A137" s="115"/>
-      <c r="B137" s="1" t="s">
+    <row r="139" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A139" s="89"/>
+      <c r="B139" s="1" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="138" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A138" s="115"/>
-      <c r="B138" s="1" t="s">
+    <row r="140" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A140" s="88" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="139" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A139" s="115"/>
-      <c r="B139" s="1" t="s">
+      <c r="B140" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="140" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A140" s="114" t="s">
+    <row r="141" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A141" s="89"/>
+      <c r="B141" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B140" s="1" t="s">
+    </row>
+    <row r="142" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A142" s="89"/>
+      <c r="B142" s="1" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="141" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A141" s="115"/>
-      <c r="B141" s="1" t="s">
+    <row r="143" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A143" s="89"/>
+      <c r="B143" s="1" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="142" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A142" s="115"/>
-      <c r="B142" s="1" t="s">
+    <row r="144" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A144" s="89"/>
+      <c r="B144" s="1" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="143" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A143" s="115"/>
-      <c r="B143" s="1" t="s">
+    <row r="145" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A145" s="89"/>
+      <c r="B145" s="1" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="144" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A144" s="115"/>
-      <c r="B144" s="1" t="s">
+    <row r="146" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A146" s="89"/>
+      <c r="B146" s="1" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="145" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A145" s="115"/>
-      <c r="B145" s="1" t="s">
+    <row r="147" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A147" s="89"/>
+      <c r="B147" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="146" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A146" s="115"/>
-      <c r="B146" s="1" t="s">
+    <row r="148" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A148" s="89"/>
+      <c r="B148" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="147" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A147" s="115"/>
-      <c r="B147" s="1" t="s">
+    <row r="149" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A149" s="89"/>
+      <c r="B149" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="148" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A148" s="115"/>
-      <c r="B148" s="1" t="s">
+    <row r="150" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A150" s="89"/>
+      <c r="B150" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="149" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A149" s="115"/>
-      <c r="B149" s="1" t="s">
+    <row r="151" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A151" s="89"/>
+      <c r="B151" s="1" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="150" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A150" s="115"/>
-      <c r="B150" s="1" t="s">
+    <row r="152" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A152" s="89"/>
+      <c r="B152" s="1" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="151" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A151" s="115"/>
-      <c r="B151" s="1" t="s">
+    <row r="153" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A153" s="89"/>
+      <c r="B153" s="1" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="152" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A152" s="115"/>
-      <c r="B152" s="1" t="s">
+    <row r="154" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A154" s="89"/>
+      <c r="B154" s="1" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="153" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A153" s="115"/>
-      <c r="B153" s="1" t="s">
+    <row r="155" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A155" s="89"/>
+      <c r="B155" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="154" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A154" s="115"/>
-      <c r="B154" s="1" t="s">
+    <row r="156" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A156" s="89"/>
+      <c r="B156" s="1" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="155" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A155" s="115"/>
-      <c r="B155" s="1" t="s">
+    <row r="157" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A157" s="89"/>
+      <c r="B157" s="1" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="156" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A156" s="115"/>
-      <c r="B156" s="1" t="s">
+    <row r="158" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A158" s="88" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="157" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A157" s="115"/>
-      <c r="B157" s="1" t="s">
+      <c r="B158" s="1" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="158" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A158" s="114" t="s">
+    <row r="159" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A159" s="89"/>
+      <c r="B159" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B158" s="1" t="s">
+    </row>
+    <row r="160" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A160" s="89"/>
+      <c r="B160" s="1" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="159" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A159" s="115"/>
-      <c r="B159" s="1" t="s">
+    <row r="161" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A161" s="89"/>
+      <c r="B161" s="1" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="160" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A160" s="115"/>
-      <c r="B160" s="1" t="s">
+    <row r="162" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A162" s="89"/>
+      <c r="B162" s="1" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="161" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A161" s="115"/>
-      <c r="B161" s="1" t="s">
+    <row r="163" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A163" s="89"/>
+      <c r="B163" s="1" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="162" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A162" s="115"/>
-      <c r="B162" s="1" t="s">
+    <row r="164" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A164" s="89"/>
+      <c r="B164" s="1" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="163" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A163" s="115"/>
-      <c r="B163" s="1" t="s">
+    <row r="165" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A165" s="89"/>
+      <c r="B165" s="1" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="164" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A164" s="115"/>
-      <c r="B164" s="1" t="s">
+    <row r="166" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A166" s="89"/>
+      <c r="B166" s="1" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="165" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A165" s="115"/>
-      <c r="B165" s="1" t="s">
+    <row r="167" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A167" s="89"/>
+      <c r="B167" s="1" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="166" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A166" s="115"/>
-      <c r="B166" s="1" t="s">
+    <row r="168" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A168" s="89"/>
+      <c r="B168" s="1" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="167" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A167" s="115"/>
-      <c r="B167" s="1" t="s">
+    <row r="169" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A169" s="89"/>
+      <c r="B169" s="1" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="168" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A168" s="115"/>
-      <c r="B168" s="1" t="s">
+    <row r="170" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A170" s="89"/>
+      <c r="B170" s="1" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="169" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A169" s="115"/>
-      <c r="B169" s="1" t="s">
+    <row r="171" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A171" s="89"/>
+      <c r="B171" s="1" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="170" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A170" s="115"/>
-      <c r="B170" s="1" t="s">
+    <row r="172" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A172" s="88" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="171" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A171" s="115"/>
-      <c r="B171" s="1" t="s">
+      <c r="B172" s="1" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="172" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A172" s="114" t="s">
+    <row r="173" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A173" s="89"/>
+      <c r="B173" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="B172" s="1" t="s">
+    </row>
+    <row r="174" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A174" s="89"/>
+      <c r="B174" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="173" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A173" s="115"/>
-      <c r="B173" s="1" t="s">
+    <row r="175" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A175" s="89"/>
+      <c r="B175" s="1" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="174" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A174" s="115"/>
-      <c r="B174" s="1" t="s">
+    <row r="176" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A176" s="89"/>
+      <c r="B176" s="1" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="175" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A175" s="115"/>
-      <c r="B175" s="1" t="s">
+    <row r="177" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A177" s="89"/>
+      <c r="B177" s="1" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="176" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A176" s="115"/>
-      <c r="B176" s="1" t="s">
+    <row r="178" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A178" s="89"/>
+      <c r="B178" s="1" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="177" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A177" s="115"/>
-      <c r="B177" s="1" t="s">
+    <row r="179" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A179" s="88" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="178" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A178" s="115"/>
-      <c r="B178" s="1" t="s">
+      <c r="B179" s="1" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="179" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A179" s="114" t="s">
+    <row r="180" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A180" s="89"/>
+      <c r="B180" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="B179" s="1" t="s">
+    </row>
+    <row r="181" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A181" s="89"/>
+      <c r="B181" s="1" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="180" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A180" s="115"/>
-      <c r="B180" s="1" t="s">
+    <row r="182" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A182" s="89"/>
+      <c r="B182" s="1" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="181" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A181" s="115"/>
-      <c r="B181" s="1" t="s">
+    <row r="183" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A183" s="89"/>
+      <c r="B183" s="1" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="182" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A182" s="115"/>
-      <c r="B182" s="1" t="s">
+    <row r="184" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A184" s="88" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="183" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A183" s="115"/>
-      <c r="B183" s="1" t="s">
+      <c r="B184" s="1" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="184" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A184" s="114" t="s">
+    <row r="185" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A185" s="89"/>
+      <c r="B185" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B184" s="1" t="s">
+    </row>
+    <row r="186" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A186" s="89"/>
+      <c r="B186" s="1" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="185" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A185" s="115"/>
-      <c r="B185" s="1" t="s">
+    <row r="187" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A187" s="89"/>
+      <c r="B187" s="1" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="186" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A186" s="115"/>
-      <c r="B186" s="1" t="s">
+    <row r="188" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A188" s="89"/>
+      <c r="B188" s="1" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="187" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A187" s="115"/>
-      <c r="B187" s="1" t="s">
+    <row r="189" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A189" s="88" t="s">
+        <v>84</v>
+      </c>
+      <c r="B189" s="1" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="188" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A188" s="115"/>
-      <c r="B188" s="1" t="s">
+    <row r="190" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A190" s="89"/>
+      <c r="B190" s="1" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="189" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A189" s="114" t="s">
-        <v>86</v>
-      </c>
-      <c r="B189" s="1" t="s">
+    <row r="191" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A191" s="89"/>
+      <c r="B191" s="1" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="190" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A190" s="115"/>
-      <c r="B190" s="1" t="s">
+    <row r="192" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A192" s="88" t="s">
+        <v>80</v>
+      </c>
+      <c r="B192" s="1" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="191" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A191" s="115"/>
-      <c r="B191" s="1" t="s">
+    <row r="193" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A193" s="89"/>
+      <c r="B193" s="1" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="192" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A192" s="114" t="s">
-        <v>82</v>
-      </c>
-      <c r="B192" s="1" t="s">
+    <row r="194" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A194" s="89"/>
+      <c r="B194" s="1" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="193" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A193" s="115"/>
-      <c r="B193" s="1" t="s">
+    <row r="195" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A195" s="89"/>
+      <c r="B195" s="1" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="194" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A194" s="115"/>
-      <c r="B194" s="1" t="s">
+    <row r="196" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A196" s="89"/>
+      <c r="B196" s="1" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="195" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A195" s="115"/>
-      <c r="B195" s="1" t="s">
+    <row r="197" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A197" s="89"/>
+      <c r="B197" s="1" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="196" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A196" s="115"/>
-      <c r="B196" s="1" t="s">
+    <row r="198" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A198" s="89"/>
+      <c r="B198" s="1" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="197" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A197" s="115"/>
-      <c r="B197" s="1" t="s">
+    <row r="199" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A199" s="89"/>
+      <c r="B199" s="1" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="198" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A198" s="115"/>
-      <c r="B198" s="1" t="s">
+    <row r="200" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A200" s="89"/>
+      <c r="B200" s="1" t="s">
         <v>310</v>
-      </c>
-    </row>
-    <row r="199" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A199" s="115"/>
-      <c r="B199" s="1" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A200" s="115"/>
-      <c r="B200" s="1" t="s">
-        <v>312</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A2:A24"/>
-    <mergeCell ref="A25:A32"/>
-    <mergeCell ref="A33:A47"/>
-    <mergeCell ref="A48:A54"/>
-    <mergeCell ref="A55:A66"/>
-    <mergeCell ref="A67:A76"/>
-    <mergeCell ref="A77:A124"/>
-    <mergeCell ref="A125:A133"/>
-    <mergeCell ref="A134:A139"/>
-    <mergeCell ref="A140:A157"/>
     <mergeCell ref="A192:A200"/>
     <mergeCell ref="A158:A171"/>
     <mergeCell ref="A172:A178"/>
     <mergeCell ref="A179:A183"/>
     <mergeCell ref="A184:A188"/>
     <mergeCell ref="A189:A191"/>
+    <mergeCell ref="A67:A76"/>
+    <mergeCell ref="A77:A124"/>
+    <mergeCell ref="A125:A133"/>
+    <mergeCell ref="A134:A139"/>
+    <mergeCell ref="A140:A157"/>
+    <mergeCell ref="A2:A24"/>
+    <mergeCell ref="A25:A32"/>
+    <mergeCell ref="A33:A47"/>
+    <mergeCell ref="A48:A54"/>
+    <mergeCell ref="A55:A66"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
